--- a/Region_results/Region_Forecasting_26_0701_0707.xlsx
+++ b/Region_results/Region_Forecasting_26_0701_0707.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lena/forecasting_new/Region_results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B766177D-33A0-354E-83D7-B0764F9FAC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE92A384-F57C-244F-A73E-6ED2C1CA71CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3209,7 +3209,7 @@
       <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2">
         <v>299</v>
       </c>
     </row>
@@ -3220,8 +3220,8 @@
       <c r="B3" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C3" s="5">
-        <v>322.42242431640619</v>
+      <c r="C3">
+        <v>322.42</v>
       </c>
       <c r="D3">
         <v>253.69171142578119</v>
@@ -3234,8 +3234,8 @@
       <c r="B4" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C4" s="5">
-        <v>345.14096069335938</v>
+      <c r="C4">
+        <v>345.14</v>
       </c>
       <c r="D4">
         <v>288.16900634765619</v>
@@ -3248,8 +3248,8 @@
       <c r="B5" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C5" s="5">
-        <v>278.01104736328119</v>
+      <c r="C5">
+        <v>320.55</v>
       </c>
       <c r="D5">
         <v>242.49076843261719</v>
@@ -3262,8 +3262,8 @@
       <c r="B6" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C6" s="5">
-        <v>237.49482727050781</v>
+      <c r="C6">
+        <v>277.44</v>
       </c>
       <c r="D6">
         <v>217.30253601074219</v>
@@ -3276,8 +3276,8 @@
       <c r="B7" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="5">
-        <v>316.32479858398438</v>
+      <c r="C7">
+        <v>316.32</v>
       </c>
       <c r="D7">
         <v>261.15060424804688</v>
@@ -3290,8 +3290,8 @@
       <c r="B8" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="5">
-        <v>342.00030517578119</v>
+      <c r="C8">
+        <v>342</v>
       </c>
       <c r="D8">
         <v>283.59762573242188</v>
@@ -3304,7 +3304,7 @@
       <c r="B9" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9">
         <v>253</v>
       </c>
     </row>
@@ -3315,8 +3315,8 @@
       <c r="B10" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="5">
-        <v>261.64144897460938</v>
+      <c r="C10">
+        <v>261.64</v>
       </c>
       <c r="D10">
         <v>204.4527893066406</v>
@@ -3329,8 +3329,8 @@
       <c r="B11" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C11" s="5">
-        <v>271.45809936523438</v>
+      <c r="C11">
+        <v>271.45999999999998</v>
       </c>
       <c r="D11">
         <v>206.3299560546875</v>
@@ -3343,8 +3343,8 @@
       <c r="B12" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C12" s="5">
-        <v>224.59162902832031</v>
+      <c r="C12">
+        <v>258.95999999999998</v>
       </c>
       <c r="D12">
         <v>192.73992919921881</v>
@@ -3357,8 +3357,8 @@
       <c r="B13" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="5">
-        <v>190.61805725097659</v>
+      <c r="C13">
+        <v>222.68</v>
       </c>
       <c r="D13">
         <v>166.74845886230469</v>
@@ -3371,8 +3371,8 @@
       <c r="B14" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C14" s="5">
-        <v>258.074951171875</v>
+      <c r="C14">
+        <v>258.07</v>
       </c>
       <c r="D14">
         <v>197.15086364746091</v>
@@ -3385,8 +3385,8 @@
       <c r="B15" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C15" s="5">
-        <v>283.54226684570312</v>
+      <c r="C15">
+        <v>283.54000000000002</v>
       </c>
       <c r="D15">
         <v>218.03691101074219</v>
@@ -3399,7 +3399,7 @@
       <c r="B16" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16">
         <v>231</v>
       </c>
     </row>
@@ -3410,8 +3410,8 @@
       <c r="B17" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="5">
-        <v>271.26742553710938</v>
+      <c r="C17">
+        <v>271.27</v>
       </c>
       <c r="D17">
         <v>217.21189880371091</v>
@@ -3424,8 +3424,8 @@
       <c r="B18" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="5">
-        <v>264.33197021484381</v>
+      <c r="C18">
+        <v>264.33</v>
       </c>
       <c r="D18">
         <v>221.97235107421881</v>
@@ -3438,8 +3438,8 @@
       <c r="B19" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C19" s="5">
-        <v>198.8806457519531</v>
+      <c r="C19">
+        <v>229.31</v>
       </c>
       <c r="D19">
         <v>166.2480773925781</v>
@@ -3452,8 +3452,8 @@
       <c r="B20" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="5">
-        <v>186.1312255859375</v>
+      <c r="C20">
+        <v>217.44</v>
       </c>
       <c r="D20">
         <v>157.12757873535159</v>
@@ -3466,8 +3466,8 @@
       <c r="B21" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="5">
-        <v>224.704833984375</v>
+      <c r="C21">
+        <v>224.7</v>
       </c>
       <c r="D21">
         <v>171.0025939941406</v>
@@ -3480,8 +3480,8 @@
       <c r="B22" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="5">
-        <v>263.50289916992188</v>
+      <c r="C22">
+        <v>263.5</v>
       </c>
       <c r="D22">
         <v>223.53059387207031</v>
@@ -3494,7 +3494,7 @@
       <c r="B23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23">
         <v>277</v>
       </c>
     </row>
@@ -3505,8 +3505,8 @@
       <c r="B24" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C24" s="5">
-        <v>309.15036010742188</v>
+      <c r="C24">
+        <v>309.14999999999998</v>
       </c>
       <c r="D24">
         <v>246.57273864746091</v>
@@ -3519,8 +3519,8 @@
       <c r="B25" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C25" s="5">
-        <v>316.9503173828125</v>
+      <c r="C25">
+        <v>316.95</v>
       </c>
       <c r="D25">
         <v>254.05339050292969</v>
@@ -3533,8 +3533,8 @@
       <c r="B26" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C26" s="5">
-        <v>214.8381652832031</v>
+      <c r="C26">
+        <v>247.71</v>
       </c>
       <c r="D26">
         <v>172.8209533691406</v>
@@ -3547,8 +3547,8 @@
       <c r="B27" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C27" s="5">
-        <v>201.45155334472659</v>
+      <c r="C27">
+        <v>235.34</v>
       </c>
       <c r="D27">
         <v>169.92646789550781</v>
@@ -3561,8 +3561,8 @@
       <c r="B28" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C28" s="5">
-        <v>267.05654907226562</v>
+      <c r="C28">
+        <v>267.06</v>
       </c>
       <c r="D28">
         <v>212.11738586425781</v>
@@ -3575,8 +3575,8 @@
       <c r="B29" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C29" s="5">
-        <v>277.89718627929688</v>
+      <c r="C29">
+        <v>277.89999999999998</v>
       </c>
       <c r="D29">
         <v>230.63883972167969</v>
@@ -3589,7 +3589,7 @@
       <c r="B30" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30">
         <v>162</v>
       </c>
     </row>
@@ -3600,8 +3600,8 @@
       <c r="B31" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C31" s="5">
-        <v>206.81919860839841</v>
+      <c r="C31">
+        <v>206.82</v>
       </c>
       <c r="D31">
         <v>170.75885009765619</v>
@@ -3614,8 +3614,8 @@
       <c r="B32" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C32" s="5">
-        <v>200.9578857421875</v>
+      <c r="C32">
+        <v>200.96</v>
       </c>
       <c r="D32">
         <v>168.63731384277341</v>
@@ -3628,8 +3628,8 @@
       <c r="B33" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C33" s="5">
-        <v>155.76966857910159</v>
+      <c r="C33">
+        <v>179.6</v>
       </c>
       <c r="D33">
         <v>129.78892517089841</v>
@@ -3642,8 +3642,8 @@
       <c r="B34" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C34" s="5">
-        <v>121.9946594238281</v>
+      <c r="C34">
+        <v>142.52000000000001</v>
       </c>
       <c r="D34">
         <v>108.6866912841797</v>
@@ -3656,8 +3656,8 @@
       <c r="B35" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C35" s="5">
-        <v>174.49092102050781</v>
+      <c r="C35">
+        <v>174.49</v>
       </c>
       <c r="D35">
         <v>143.1414489746094</v>
@@ -3670,8 +3670,8 @@
       <c r="B36" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C36" s="5">
-        <v>196.2839660644531</v>
+      <c r="C36">
+        <v>196.28</v>
       </c>
       <c r="D36">
         <v>169.62980651855469</v>
@@ -3684,7 +3684,7 @@
       <c r="B37" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C37" s="5">
+      <c r="C37">
         <v>227</v>
       </c>
     </row>
@@ -3695,8 +3695,8 @@
       <c r="B38" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C38" s="5">
-        <v>242.70240783691409</v>
+      <c r="C38">
+        <v>242.7</v>
       </c>
       <c r="D38">
         <v>196.6839904785156</v>
@@ -3709,8 +3709,8 @@
       <c r="B39" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C39" s="5">
-        <v>241.14350891113281</v>
+      <c r="C39">
+        <v>241.14</v>
       </c>
       <c r="D39">
         <v>195.34819030761719</v>
@@ -3723,8 +3723,8 @@
       <c r="B40" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C40" s="5">
-        <v>202.3319396972656</v>
+      <c r="C40">
+        <v>233.29</v>
       </c>
       <c r="D40">
         <v>175.12544250488281</v>
@@ -3737,8 +3737,8 @@
       <c r="B41" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C41" s="5">
-        <v>158.9185485839844</v>
+      <c r="C41">
+        <v>185.65</v>
       </c>
       <c r="D41">
         <v>144.6434631347656</v>
@@ -3751,8 +3751,8 @@
       <c r="B42" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C42" s="5">
-        <v>217.40301513671881</v>
+      <c r="C42">
+        <v>217.4</v>
       </c>
       <c r="D42">
         <v>174.8548889160156</v>
@@ -3765,8 +3765,8 @@
       <c r="B43" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C43" s="5">
-        <v>231.83171081542969</v>
+      <c r="C43">
+        <v>231.83</v>
       </c>
       <c r="D43">
         <v>195.54368591308591</v>
@@ -3779,7 +3779,7 @@
       <c r="B44" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C44" s="5">
+      <c r="C44">
         <v>316</v>
       </c>
     </row>
@@ -3790,8 +3790,8 @@
       <c r="B45" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C45" s="5">
-        <v>369.775390625</v>
+      <c r="C45">
+        <v>369.78</v>
       </c>
       <c r="D45">
         <v>290.32455444335938</v>
@@ -3804,8 +3804,8 @@
       <c r="B46" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C46" s="5">
-        <v>367.79840087890619</v>
+      <c r="C46">
+        <v>367.8</v>
       </c>
       <c r="D46">
         <v>297.500732421875</v>
@@ -3818,8 +3818,8 @@
       <c r="B47" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C47" s="5">
-        <v>296.1014404296875</v>
+      <c r="C47">
+        <v>341.41</v>
       </c>
       <c r="D47">
         <v>241.0497741699219</v>
@@ -3832,8 +3832,8 @@
       <c r="B48" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C48" s="5">
-        <v>235.82464599609381</v>
+      <c r="C48">
+        <v>275.49</v>
       </c>
       <c r="D48">
         <v>212.44587707519531</v>
@@ -3846,8 +3846,8 @@
       <c r="B49" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C49" s="5">
-        <v>314.91107177734381</v>
+      <c r="C49">
+        <v>314.91000000000003</v>
       </c>
       <c r="D49">
         <v>246.66825866699219</v>
@@ -3860,8 +3860,8 @@
       <c r="B50" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C50" s="5">
-        <v>357.82196044921881</v>
+      <c r="C50">
+        <v>357.82</v>
       </c>
       <c r="D50">
         <v>292.55963134765619</v>
@@ -3874,7 +3874,7 @@
       <c r="B51" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C51" s="5">
+      <c r="C51">
         <v>260</v>
       </c>
     </row>
@@ -3885,8 +3885,8 @@
       <c r="B52" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C52" s="5">
-        <v>306.26651000976562</v>
+      <c r="C52">
+        <v>306.27</v>
       </c>
       <c r="D52">
         <v>221.67633056640619</v>
@@ -3899,8 +3899,8 @@
       <c r="B53" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C53" s="5">
-        <v>296.201904296875</v>
+      <c r="C53">
+        <v>296.2</v>
       </c>
       <c r="D53">
         <v>223.5021057128906</v>
@@ -3913,8 +3913,8 @@
       <c r="B54" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C54" s="5">
-        <v>212.0948181152344</v>
+      <c r="C54">
+        <v>244.55</v>
       </c>
       <c r="D54">
         <v>184.46409606933591</v>
@@ -3927,8 +3927,8 @@
       <c r="B55" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C55" s="5">
-        <v>180.9033508300781</v>
+      <c r="C55">
+        <v>211.33</v>
       </c>
       <c r="D55">
         <v>158.46501159667969</v>
@@ -3941,8 +3941,8 @@
       <c r="B56" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C56" s="5">
-        <v>268.73275756835938</v>
+      <c r="C56">
+        <v>268.73</v>
       </c>
       <c r="D56">
         <v>193.0555725097656</v>
@@ -3955,8 +3955,8 @@
       <c r="B57" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C57" s="5">
-        <v>281.70217895507812</v>
+      <c r="C57">
+        <v>281.7</v>
       </c>
       <c r="D57">
         <v>218.6914978027344</v>
@@ -3969,7 +3969,7 @@
       <c r="B58" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C58" s="5">
+      <c r="C58">
         <v>694</v>
       </c>
     </row>
@@ -3980,8 +3980,8 @@
       <c r="B59" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C59" s="5">
-        <v>748.0379638671875</v>
+      <c r="C59">
+        <v>748.04</v>
       </c>
       <c r="D59">
         <v>600.67437744140625</v>
@@ -3994,8 +3994,8 @@
       <c r="B60" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C60" s="5">
-        <v>722.87176513671875</v>
+      <c r="C60">
+        <v>722.87</v>
       </c>
       <c r="D60">
         <v>604.00299072265625</v>
@@ -4008,8 +4008,8 @@
       <c r="B61" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C61" s="5">
-        <v>590.669921875</v>
+      <c r="C61">
+        <v>681.05</v>
       </c>
       <c r="D61">
         <v>502.13525390625</v>
@@ -4022,8 +4022,8 @@
       <c r="B62" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C62" s="5">
-        <v>490.3587646484375</v>
+      <c r="C62">
+        <v>572.84</v>
       </c>
       <c r="D62">
         <v>440.6446533203125</v>
@@ -4036,8 +4036,8 @@
       <c r="B63" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C63" s="5">
-        <v>649.8055419921875</v>
+      <c r="C63">
+        <v>649.80999999999995</v>
       </c>
       <c r="D63">
         <v>533.2020263671875</v>
@@ -4050,8 +4050,8 @@
       <c r="B64" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C64" s="5">
-        <v>719.60797119140625</v>
+      <c r="C64">
+        <v>719.61</v>
       </c>
       <c r="D64">
         <v>610.9962158203125</v>
@@ -4064,7 +4064,7 @@
       <c r="B65" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C65" s="5">
+      <c r="C65">
         <v>498</v>
       </c>
     </row>
@@ -4075,8 +4075,8 @@
       <c r="B66" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C66" s="5">
-        <v>504.40371704101562</v>
+      <c r="C66">
+        <v>504.4</v>
       </c>
       <c r="D66">
         <v>362.69915771484381</v>
@@ -4089,8 +4089,8 @@
       <c r="B67" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C67" s="5">
-        <v>492.827880859375</v>
+      <c r="C67">
+        <v>492.83</v>
       </c>
       <c r="D67">
         <v>379.75506591796881</v>
@@ -4103,8 +4103,8 @@
       <c r="B68" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C68" s="5">
-        <v>390.45126342773438</v>
+      <c r="C68">
+        <v>450.19</v>
       </c>
       <c r="D68">
         <v>318.41827392578119</v>
@@ -4117,8 +4117,8 @@
       <c r="B69" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C69" s="5">
-        <v>363.34625244140619</v>
+      <c r="C69">
+        <v>424.46</v>
       </c>
       <c r="D69">
         <v>323.82965087890619</v>
@@ -4131,8 +4131,8 @@
       <c r="B70" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C70" s="5">
-        <v>501.08505249023438</v>
+      <c r="C70">
+        <v>501.09</v>
       </c>
       <c r="D70">
         <v>362.34555053710938</v>
@@ -4145,8 +4145,8 @@
       <c r="B71" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C71" s="5">
-        <v>475.09957885742188</v>
+      <c r="C71">
+        <v>475.1</v>
       </c>
       <c r="D71">
         <v>414.18539428710938</v>
@@ -4159,7 +4159,7 @@
       <c r="B72" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C72" s="5">
+      <c r="C72">
         <v>215</v>
       </c>
     </row>
@@ -4170,8 +4170,8 @@
       <c r="B73" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C73" s="5">
-        <v>218.31678771972659</v>
+      <c r="C73">
+        <v>218.32</v>
       </c>
       <c r="D73">
         <v>170.61460876464841</v>
@@ -4184,8 +4184,8 @@
       <c r="B74" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C74" s="5">
-        <v>254.06312561035159</v>
+      <c r="C74">
+        <v>254.06</v>
       </c>
       <c r="D74">
         <v>195.84428405761719</v>
@@ -4198,8 +4198,8 @@
       <c r="B75" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C75" s="5">
-        <v>188.87809753417969</v>
+      <c r="C75">
+        <v>217.78</v>
       </c>
       <c r="D75">
         <v>159.8675231933594</v>
@@ -4212,8 +4212,8 @@
       <c r="B76" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C76" s="5">
-        <v>149.6490783691406</v>
+      <c r="C76">
+        <v>174.82</v>
       </c>
       <c r="D76">
         <v>128.48634338378909</v>
@@ -4226,8 +4226,8 @@
       <c r="B77" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C77" s="5">
-        <v>213.35966491699219</v>
+      <c r="C77">
+        <v>213.36</v>
       </c>
       <c r="D77">
         <v>158.37257385253909</v>
@@ -4240,8 +4240,8 @@
       <c r="B78" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C78" s="5">
-        <v>228.07218933105469</v>
+      <c r="C78">
+        <v>228.07</v>
       </c>
       <c r="D78">
         <v>193.28741455078119</v>
@@ -4254,7 +4254,7 @@
       <c r="B79" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C79" s="5">
+      <c r="C79">
         <v>207</v>
       </c>
     </row>
@@ -4265,8 +4265,8 @@
       <c r="B80" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C80" s="5">
-        <v>196.3484191894531</v>
+      <c r="C80">
+        <v>196.35</v>
       </c>
       <c r="D80">
         <v>147.59443664550781</v>
@@ -4279,8 +4279,8 @@
       <c r="B81" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C81" s="5">
-        <v>209.79887390136719</v>
+      <c r="C81">
+        <v>209.8</v>
       </c>
       <c r="D81">
         <v>155.9042053222656</v>
@@ -4293,8 +4293,8 @@
       <c r="B82" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C82" s="5">
-        <v>162.3913879394531</v>
+      <c r="C82">
+        <v>187.24</v>
       </c>
       <c r="D82">
         <v>140.1158447265625</v>
@@ -4307,8 +4307,8 @@
       <c r="B83" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C83" s="5">
-        <v>128.8943176269531</v>
+      <c r="C83">
+        <v>150.58000000000001</v>
       </c>
       <c r="D83">
         <v>116.4039688110352</v>
@@ -4321,8 +4321,8 @@
       <c r="B84" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C84" s="5">
-        <v>191.31648254394531</v>
+      <c r="C84">
+        <v>191.32</v>
       </c>
       <c r="D84">
         <v>139.31416320800781</v>
@@ -4335,8 +4335,8 @@
       <c r="B85" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C85" s="5">
-        <v>215.3611145019531</v>
+      <c r="C85">
+        <v>215.36</v>
       </c>
       <c r="D85">
         <v>174.06658935546881</v>
@@ -4349,7 +4349,7 @@
       <c r="B86" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C86" s="5">
+      <c r="C86">
         <v>328</v>
       </c>
     </row>
@@ -4360,8 +4360,8 @@
       <c r="B87" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C87" s="5">
-        <v>383.681396484375</v>
+      <c r="C87">
+        <v>383.68</v>
       </c>
       <c r="D87">
         <v>307.16259765625</v>
@@ -4374,8 +4374,8 @@
       <c r="B88" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C88" s="5">
-        <v>385.6448974609375</v>
+      <c r="C88">
+        <v>385.64</v>
       </c>
       <c r="D88">
         <v>311.61734008789062</v>
@@ -4388,8 +4388,8 @@
       <c r="B89" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C89" s="5">
-        <v>288.385009765625</v>
+      <c r="C89">
+        <v>332.51</v>
       </c>
       <c r="D89">
         <v>249.29261779785159</v>
@@ -4402,8 +4402,8 @@
       <c r="B90" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C90" s="5">
-        <v>257.03390502929688</v>
+      <c r="C90">
+        <v>300.27</v>
       </c>
       <c r="D90">
         <v>222.31634521484381</v>
@@ -4416,8 +4416,8 @@
       <c r="B91" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C91" s="5">
-        <v>339.51303100585938</v>
+      <c r="C91">
+        <v>339.51</v>
       </c>
       <c r="D91">
         <v>274.6192626953125</v>
@@ -4430,8 +4430,8 @@
       <c r="B92" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C92" s="5">
-        <v>364.0181884765625</v>
+      <c r="C92">
+        <v>364.02</v>
       </c>
       <c r="D92">
         <v>309.55984497070312</v>
@@ -4444,7 +4444,7 @@
       <c r="B93" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C93" s="5">
+      <c r="C93">
         <v>449</v>
       </c>
     </row>
@@ -4455,8 +4455,8 @@
       <c r="B94" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C94" s="5">
-        <v>436.02456665039062</v>
+      <c r="C94">
+        <v>436.02</v>
       </c>
       <c r="D94">
         <v>325.227294921875</v>
@@ -4469,8 +4469,8 @@
       <c r="B95" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C95" s="5">
-        <v>441.24441528320312</v>
+      <c r="C95">
+        <v>441.24</v>
       </c>
       <c r="D95">
         <v>365.365234375</v>
@@ -4483,8 +4483,8 @@
       <c r="B96" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C96" s="5">
-        <v>357.24343872070312</v>
+      <c r="C96">
+        <v>411.9</v>
       </c>
       <c r="D96">
         <v>287.76388549804688</v>
@@ -4497,8 +4497,8 @@
       <c r="B97" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C97" s="5">
-        <v>297.16046142578119</v>
+      <c r="C97">
+        <v>347.15</v>
       </c>
       <c r="D97">
         <v>268.35089111328119</v>
@@ -4511,8 +4511,8 @@
       <c r="B98" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C98" s="5">
-        <v>411.33978271484381</v>
+      <c r="C98">
+        <v>411.34</v>
       </c>
       <c r="D98">
         <v>309.12271118164062</v>
@@ -4525,8 +4525,8 @@
       <c r="B99" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C99" s="5">
-        <v>425.7193603515625</v>
+      <c r="C99">
+        <v>425.72</v>
       </c>
       <c r="D99">
         <v>329.67800903320312</v>
@@ -4539,7 +4539,7 @@
       <c r="B100" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C100" s="5">
+      <c r="C100">
         <v>250</v>
       </c>
     </row>
@@ -4550,8 +4550,8 @@
       <c r="B101" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C101" s="5">
-        <v>270.68954467773438</v>
+      <c r="C101">
+        <v>270.69</v>
       </c>
       <c r="D101">
         <v>217.59065246582031</v>
@@ -4564,8 +4564,8 @@
       <c r="B102" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C102" s="5">
-        <v>264.69976806640619</v>
+      <c r="C102">
+        <v>264.7</v>
       </c>
       <c r="D102">
         <v>219.59931945800781</v>
@@ -4578,8 +4578,8 @@
       <c r="B103" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C103" s="5">
-        <v>190.43321228027341</v>
+      <c r="C103">
+        <v>219.57</v>
       </c>
       <c r="D103">
         <v>164.22172546386719</v>
@@ -4592,8 +4592,8 @@
       <c r="B104" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C104" s="5">
-        <v>166.56842041015619</v>
+      <c r="C104">
+        <v>194.59</v>
       </c>
       <c r="D104">
         <v>150.32411193847659</v>
@@ -4606,8 +4606,8 @@
       <c r="B105" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C105" s="5">
-        <v>232.5799865722656</v>
+      <c r="C105">
+        <v>232.58</v>
       </c>
       <c r="D105">
         <v>190.19465637207031</v>
@@ -4620,8 +4620,8 @@
       <c r="B106" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C106" s="5">
-        <v>255.30291748046881</v>
+      <c r="C106">
+        <v>255.3</v>
       </c>
       <c r="D106">
         <v>215.86247253417969</v>
@@ -4634,7 +4634,7 @@
       <c r="B107" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C107" s="5">
+      <c r="C107">
         <v>224</v>
       </c>
     </row>
@@ -4645,8 +4645,8 @@
       <c r="B108" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C108" s="5">
-        <v>243.55755615234381</v>
+      <c r="C108">
+        <v>243.56</v>
       </c>
       <c r="D108">
         <v>199.1874084472656</v>
@@ -4659,8 +4659,8 @@
       <c r="B109" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C109" s="5">
-        <v>254.7274475097656</v>
+      <c r="C109">
+        <v>254.73</v>
       </c>
       <c r="D109">
         <v>202.97889709472659</v>
@@ -4673,8 +4673,8 @@
       <c r="B110" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C110" s="5">
-        <v>178.53070068359381</v>
+      <c r="C110">
+        <v>205.85</v>
       </c>
       <c r="D110">
         <v>156.84635925292969</v>
@@ -4687,8 +4687,8 @@
       <c r="B111" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C111" s="5">
-        <v>158.7364807128906</v>
+      <c r="C111">
+        <v>185.44</v>
       </c>
       <c r="D111">
         <v>136.2252502441406</v>
@@ -4701,8 +4701,8 @@
       <c r="B112" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C112" s="5">
-        <v>211.15193176269531</v>
+      <c r="C112">
+        <v>211.15</v>
       </c>
       <c r="D112">
         <v>175.94195556640619</v>
@@ -4715,8 +4715,8 @@
       <c r="B113" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C113" s="5">
-        <v>245.4575500488281</v>
+      <c r="C113">
+        <v>245.46</v>
       </c>
       <c r="D113">
         <v>200.43084716796881</v>
@@ -4729,7 +4729,7 @@
       <c r="B114" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C114" s="5">
+      <c r="C114">
         <v>255</v>
       </c>
     </row>
@@ -4740,8 +4740,8 @@
       <c r="B115" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C115" s="5">
-        <v>268.98779296875</v>
+      <c r="C115">
+        <v>268.99</v>
       </c>
       <c r="D115">
         <v>221.35514831542969</v>
@@ -4754,8 +4754,8 @@
       <c r="B116" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C116" s="5">
-        <v>261.91622924804688</v>
+      <c r="C116">
+        <v>261.92</v>
       </c>
       <c r="D116">
         <v>223.59730529785159</v>
@@ -4768,8 +4768,8 @@
       <c r="B117" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C117" s="5">
-        <v>198.017578125</v>
+      <c r="C117">
+        <v>228.32</v>
       </c>
       <c r="D117">
         <v>186.6935119628906</v>
@@ -4782,8 +4782,8 @@
       <c r="B118" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C118" s="5">
-        <v>172.44026184082031</v>
+      <c r="C118">
+        <v>201.45</v>
       </c>
       <c r="D118">
         <v>154.26060485839841</v>
@@ -4796,8 +4796,8 @@
       <c r="B119" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C119" s="5">
-        <v>245.98094177246091</v>
+      <c r="C119">
+        <v>245.98</v>
       </c>
       <c r="D119">
         <v>203.50547790527341</v>
@@ -4810,8 +4810,8 @@
       <c r="B120" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C120" s="5">
-        <v>260.09283447265619</v>
+      <c r="C120">
+        <v>260.08999999999997</v>
       </c>
       <c r="D120">
         <v>233.05584716796881</v>
@@ -4824,7 +4824,7 @@
       <c r="B121" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C121" s="5">
+      <c r="C121">
         <v>76</v>
       </c>
     </row>
@@ -4835,8 +4835,8 @@
       <c r="B122" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C122" s="5">
-        <v>83.746658325195312</v>
+      <c r="C122">
+        <v>83.75</v>
       </c>
       <c r="D122">
         <v>68.652778625488281</v>
@@ -4849,8 +4849,8 @@
       <c r="B123" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C123" s="5">
-        <v>104.268196105957</v>
+      <c r="C123">
+        <v>104.27</v>
       </c>
       <c r="D123">
         <v>87.16796875</v>
@@ -4863,8 +4863,8 @@
       <c r="B124" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C124" s="5">
-        <v>56.491779327392578</v>
+      <c r="C124">
+        <v>65.14</v>
       </c>
       <c r="D124">
         <v>51.401901245117188</v>
@@ -4877,8 +4877,8 @@
       <c r="B125" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C125" s="5">
-        <v>57.626541137695312</v>
+      <c r="C125">
+        <v>67.319999999999993</v>
       </c>
       <c r="D125">
         <v>53.242343902587891</v>
@@ -4891,8 +4891,8 @@
       <c r="B126" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C126" s="5">
-        <v>75.491867065429688</v>
+      <c r="C126">
+        <v>75.489999999999995</v>
       </c>
       <c r="D126">
         <v>63.731010437011719</v>
@@ -4905,8 +4905,8 @@
       <c r="B127" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C127" s="5">
-        <v>95.6771240234375</v>
+      <c r="C127">
+        <v>95.68</v>
       </c>
       <c r="D127">
         <v>81.808258056640625</v>
@@ -4919,7 +4919,7 @@
       <c r="B128" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C128" s="5">
+      <c r="C128">
         <v>251</v>
       </c>
     </row>
@@ -4930,8 +4930,8 @@
       <c r="B129" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C129" s="5">
-        <v>258.06903076171881</v>
+      <c r="C129">
+        <v>258.07</v>
       </c>
       <c r="D129">
         <v>210.67256164550781</v>
@@ -4944,8 +4944,8 @@
       <c r="B130" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C130" s="5">
-        <v>250.76576232910159</v>
+      <c r="C130">
+        <v>250.77</v>
       </c>
       <c r="D130">
         <v>204.59126281738281</v>
@@ -4958,8 +4958,8 @@
       <c r="B131" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C131" s="5">
-        <v>197.69537353515619</v>
+      <c r="C131">
+        <v>227.94</v>
       </c>
       <c r="D131">
         <v>178.63920593261719</v>
@@ -4972,8 +4972,8 @@
       <c r="B132" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C132" s="5">
-        <v>156.28804016113281</v>
+      <c r="C132">
+        <v>182.58</v>
       </c>
       <c r="D132">
         <v>141.77838134765619</v>
@@ -4986,8 +4986,8 @@
       <c r="B133" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C133" s="5">
-        <v>231.71284484863281</v>
+      <c r="C133">
+        <v>231.71</v>
       </c>
       <c r="D133">
         <v>186.2668151855469</v>
@@ -5000,8 +5000,8 @@
       <c r="B134" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C134" s="5">
-        <v>260.91595458984381</v>
+      <c r="C134">
+        <v>260.92</v>
       </c>
       <c r="D134">
         <v>216.70927429199219</v>
@@ -5014,7 +5014,7 @@
       <c r="B135" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C135" s="5">
+      <c r="C135">
         <v>244</v>
       </c>
     </row>
@@ -5025,8 +5025,8 @@
       <c r="B136" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C136" s="5">
-        <v>241.55097961425781</v>
+      <c r="C136">
+        <v>241.55</v>
       </c>
       <c r="D136">
         <v>201.58201599121091</v>
@@ -5039,8 +5039,8 @@
       <c r="B137" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C137" s="5">
-        <v>230.7455749511719</v>
+      <c r="C137">
+        <v>230.75</v>
       </c>
       <c r="D137">
         <v>199.48124694824219</v>
@@ -5053,8 +5053,8 @@
       <c r="B138" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C138" s="5">
-        <v>184.0208435058594</v>
+      <c r="C138">
+        <v>212.18</v>
       </c>
       <c r="D138">
         <v>164.33119201660159</v>
@@ -5067,8 +5067,8 @@
       <c r="B139" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C139" s="5">
-        <v>154.60969543457031</v>
+      <c r="C139">
+        <v>180.62</v>
       </c>
       <c r="D139">
         <v>139.4058532714844</v>
@@ -5081,8 +5081,8 @@
       <c r="B140" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C140" s="5">
-        <v>216.5795593261719</v>
+      <c r="C140">
+        <v>216.58</v>
       </c>
       <c r="D140">
         <v>173.86018371582031</v>
@@ -5095,8 +5095,8 @@
       <c r="B141" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C141" s="5">
-        <v>232.61741638183591</v>
+      <c r="C141">
+        <v>232.62</v>
       </c>
       <c r="D141">
         <v>204.8021545410156</v>
@@ -5109,7 +5109,7 @@
       <c r="B142" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C142" s="5">
+      <c r="C142">
         <v>320</v>
       </c>
     </row>
@@ -5120,8 +5120,8 @@
       <c r="B143" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C143" s="5">
-        <v>339.94830322265619</v>
+      <c r="C143">
+        <v>339.95</v>
       </c>
       <c r="D143">
         <v>290.490478515625</v>
@@ -5134,8 +5134,8 @@
       <c r="B144" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C144" s="5">
-        <v>319.41790771484381</v>
+      <c r="C144">
+        <v>319.42</v>
       </c>
       <c r="D144">
         <v>281.10400390625</v>
@@ -5148,8 +5148,8 @@
       <c r="B145" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C145" s="5">
-        <v>253.73057556152341</v>
+      <c r="C145">
+        <v>292.55</v>
       </c>
       <c r="D145">
         <v>210.44718933105469</v>
@@ -5162,8 +5162,8 @@
       <c r="B146" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C146" s="5">
-        <v>223.84086608886719</v>
+      <c r="C146">
+        <v>261.49</v>
       </c>
       <c r="D146">
         <v>188.12384033203119</v>
@@ -5176,8 +5176,8 @@
       <c r="B147" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C147" s="5">
-        <v>327.2694091796875</v>
+      <c r="C147">
+        <v>327.27</v>
       </c>
       <c r="D147">
         <v>249.03900146484381</v>
@@ -5190,8 +5190,8 @@
       <c r="B148" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C148" s="5">
-        <v>333.3245849609375</v>
+      <c r="C148">
+        <v>333.32</v>
       </c>
       <c r="D148">
         <v>284.92276000976562</v>
@@ -5204,7 +5204,7 @@
       <c r="B149" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C149" s="5">
+      <c r="C149">
         <v>193</v>
       </c>
     </row>
@@ -5215,8 +5215,8 @@
       <c r="B150" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C150" s="5">
-        <v>204.2628173828125</v>
+      <c r="C150">
+        <v>204.26</v>
       </c>
       <c r="D150">
         <v>157.05242919921881</v>
@@ -5229,8 +5229,8 @@
       <c r="B151" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C151" s="5">
-        <v>214.80430603027341</v>
+      <c r="C151">
+        <v>214.8</v>
       </c>
       <c r="D151">
         <v>172.2408142089844</v>
@@ -5243,8 +5243,8 @@
       <c r="B152" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C152" s="5">
-        <v>166.89691162109381</v>
+      <c r="C152">
+        <v>192.43</v>
       </c>
       <c r="D152">
         <v>144.8140563964844</v>
@@ -5257,8 +5257,8 @@
       <c r="B153" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C153" s="5">
-        <v>128.2574157714844</v>
+      <c r="C153">
+        <v>149.83000000000001</v>
       </c>
       <c r="D153">
         <v>113.98065185546881</v>
@@ -5271,8 +5271,8 @@
       <c r="B154" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C154" s="5">
-        <v>194.8138427734375</v>
+      <c r="C154">
+        <v>194.81</v>
       </c>
       <c r="D154">
         <v>148.73417663574219</v>
@@ -5285,8 +5285,8 @@
       <c r="B155" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C155" s="5">
-        <v>200.86170959472659</v>
+      <c r="C155">
+        <v>200.86</v>
       </c>
       <c r="D155">
         <v>164.24488830566409</v>
@@ -5299,7 +5299,7 @@
       <c r="B156" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C156" s="5">
+      <c r="C156">
         <v>376</v>
       </c>
     </row>
@@ -5310,8 +5310,8 @@
       <c r="B157" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C157" s="5">
-        <v>348.36965942382812</v>
+      <c r="C157">
+        <v>348.37</v>
       </c>
       <c r="D157">
         <v>270.35018920898438</v>
@@ -5324,8 +5324,8 @@
       <c r="B158" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C158" s="5">
-        <v>377.76480102539062</v>
+      <c r="C158">
+        <v>377.76</v>
       </c>
       <c r="D158">
         <v>302.68008422851562</v>
@@ -5338,8 +5338,8 @@
       <c r="B159" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C159" s="5">
-        <v>296.87384033203119</v>
+      <c r="C159">
+        <v>342.3</v>
       </c>
       <c r="D159">
         <v>249.50885009765619</v>
@@ -5352,8 +5352,8 @@
       <c r="B160" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C160" s="5">
-        <v>240.48176574707031</v>
+      <c r="C160">
+        <v>280.93</v>
       </c>
       <c r="D160">
         <v>221.40541076660159</v>
@@ -5366,8 +5366,8 @@
       <c r="B161" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C161" s="5">
-        <v>333.97836303710938</v>
+      <c r="C161">
+        <v>333.98</v>
       </c>
       <c r="D161">
         <v>237.8795166015625</v>
@@ -5380,8 +5380,8 @@
       <c r="B162" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C162" s="5">
-        <v>379.91995239257812</v>
+      <c r="C162">
+        <v>379.92</v>
       </c>
       <c r="D162">
         <v>306.18402099609381</v>
@@ -5394,7 +5394,7 @@
       <c r="B163" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C163" s="5">
+      <c r="C163">
         <v>344</v>
       </c>
     </row>
@@ -5405,8 +5405,8 @@
       <c r="B164" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C164" s="5">
-        <v>375.75201416015619</v>
+      <c r="C164">
+        <v>375.75</v>
       </c>
       <c r="D164">
         <v>282.01223754882812</v>
@@ -5419,8 +5419,8 @@
       <c r="B165" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C165" s="5">
-        <v>346.87771606445312</v>
+      <c r="C165">
+        <v>346.88</v>
       </c>
       <c r="D165">
         <v>277.82644653320312</v>
@@ -5433,8 +5433,8 @@
       <c r="B166" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C166" s="5">
-        <v>274.5987548828125</v>
+      <c r="C166">
+        <v>316.61</v>
       </c>
       <c r="D166">
         <v>215.8423156738281</v>
@@ -5447,8 +5447,8 @@
       <c r="B167" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C167" s="5">
-        <v>256.48733520507812</v>
+      <c r="C167">
+        <v>299.63</v>
       </c>
       <c r="D167">
         <v>221.75566101074219</v>
@@ -5461,8 +5461,8 @@
       <c r="B168" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C168" s="5">
-        <v>377.18222045898438</v>
+      <c r="C168">
+        <v>377.18</v>
       </c>
       <c r="D168">
         <v>268.34255981445312</v>
@@ -5475,8 +5475,8 @@
       <c r="B169" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C169" s="5">
-        <v>360.05401611328119</v>
+      <c r="C169">
+        <v>360.05</v>
       </c>
       <c r="D169">
         <v>274.74151611328119</v>
@@ -5489,7 +5489,7 @@
       <c r="B170" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C170" s="5">
+      <c r="C170">
         <v>429</v>
       </c>
     </row>
@@ -5500,8 +5500,8 @@
       <c r="B171" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C171" s="5">
-        <v>440.86624145507812</v>
+      <c r="C171">
+        <v>440.87</v>
       </c>
       <c r="D171">
         <v>385.82266235351562</v>
@@ -5514,8 +5514,8 @@
       <c r="B172" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C172" s="5">
-        <v>442.60305786132812</v>
+      <c r="C172">
+        <v>442.6</v>
       </c>
       <c r="D172">
         <v>396.767822265625</v>
@@ -5528,8 +5528,8 @@
       <c r="B173" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C173" s="5">
-        <v>340.63311767578119</v>
+      <c r="C173">
+        <v>392.75</v>
       </c>
       <c r="D173">
         <v>298.46664428710938</v>
@@ -5542,8 +5542,8 @@
       <c r="B174" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C174" s="5">
-        <v>256.72821044921881</v>
+      <c r="C174">
+        <v>299.91000000000003</v>
       </c>
       <c r="D174">
         <v>238.0252380371094</v>
@@ -5556,8 +5556,8 @@
       <c r="B175" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C175" s="5">
-        <v>392.74676513671881</v>
+      <c r="C175">
+        <v>392.75</v>
       </c>
       <c r="D175">
         <v>324.804443359375</v>
@@ -5570,8 +5570,8 @@
       <c r="B176" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C176" s="5">
-        <v>422.04827880859381</v>
+      <c r="C176">
+        <v>422.05</v>
       </c>
       <c r="D176">
         <v>356.65780639648438</v>
@@ -5584,7 +5584,7 @@
       <c r="B177" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C177" s="5">
+      <c r="C177">
         <v>273</v>
       </c>
     </row>
@@ -5595,8 +5595,8 @@
       <c r="B178" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C178" s="5">
-        <v>273.14559936523438</v>
+      <c r="C178">
+        <v>273.14999999999998</v>
       </c>
       <c r="D178">
         <v>206.9670104980469</v>
@@ -5609,8 +5609,8 @@
       <c r="B179" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C179" s="5">
-        <v>270.77545166015619</v>
+      <c r="C179">
+        <v>270.77999999999997</v>
       </c>
       <c r="D179">
         <v>210.82402038574219</v>
@@ -5623,8 +5623,8 @@
       <c r="B180" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C180" s="5">
-        <v>246.81687927246091</v>
+      <c r="C180">
+        <v>284.58</v>
       </c>
       <c r="D180">
         <v>202.50421142578119</v>
@@ -5637,8 +5637,8 @@
       <c r="B181" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C181" s="5">
-        <v>211.45330810546881</v>
+      <c r="C181">
+        <v>247.02</v>
       </c>
       <c r="D181">
         <v>177.56416320800781</v>
@@ -5651,8 +5651,8 @@
       <c r="B182" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C182" s="5">
-        <v>256.73104858398438</v>
+      <c r="C182">
+        <v>256.73</v>
       </c>
       <c r="D182">
         <v>193.0724182128906</v>
@@ -5665,8 +5665,8 @@
       <c r="B183" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C183" s="5">
-        <v>266.89361572265619</v>
+      <c r="C183">
+        <v>266.89</v>
       </c>
       <c r="D183">
         <v>201.06336975097659</v>
@@ -5679,7 +5679,7 @@
       <c r="B184" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C184" s="5">
+      <c r="C184">
         <v>255</v>
       </c>
     </row>
@@ -5690,8 +5690,8 @@
       <c r="B185" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C185" s="5">
-        <v>275.46035766601562</v>
+      <c r="C185">
+        <v>275.45999999999998</v>
       </c>
       <c r="D185">
         <v>213.7052307128906</v>
@@ -5704,8 +5704,8 @@
       <c r="B186" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C186" s="5">
-        <v>255.93028259277341</v>
+      <c r="C186">
+        <v>255.93</v>
       </c>
       <c r="D186">
         <v>200.2524719238281</v>
@@ -5718,8 +5718,8 @@
       <c r="B187" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C187" s="5">
-        <v>201.70164489746091</v>
+      <c r="C187">
+        <v>232.56</v>
       </c>
       <c r="D187">
         <v>169.14013671875</v>
@@ -5732,8 +5732,8 @@
       <c r="B188" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C188" s="5">
-        <v>173.98237609863281</v>
+      <c r="C188">
+        <v>203.25</v>
       </c>
       <c r="D188">
         <v>154.30754089355469</v>
@@ -5746,8 +5746,8 @@
       <c r="B189" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C189" s="5">
-        <v>247.09898376464841</v>
+      <c r="C189">
+        <v>247.1</v>
       </c>
       <c r="D189">
         <v>176.74159240722659</v>
@@ -5760,8 +5760,8 @@
       <c r="B190" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C190" s="5">
-        <v>268.40716552734381</v>
+      <c r="C190">
+        <v>268.41000000000003</v>
       </c>
       <c r="D190">
         <v>210.95445251464841</v>
@@ -5774,7 +5774,7 @@
       <c r="B191" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C191" s="5">
+      <c r="C191">
         <v>596</v>
       </c>
     </row>
@@ -5785,8 +5785,8 @@
       <c r="B192" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C192" s="5">
-        <v>593.91168212890625</v>
+      <c r="C192">
+        <v>593.91</v>
       </c>
       <c r="D192">
         <v>456.35031127929688</v>
@@ -5799,8 +5799,8 @@
       <c r="B193" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C193" s="5">
-        <v>604.1905517578125</v>
+      <c r="C193">
+        <v>604.19000000000005</v>
       </c>
       <c r="D193">
         <v>477.70425415039062</v>
@@ -5813,8 +5813,8 @@
       <c r="B194" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C194" s="5">
-        <v>472.49551391601562</v>
+      <c r="C194">
+        <v>544.79</v>
       </c>
       <c r="D194">
         <v>420.0655517578125</v>
@@ -5827,8 +5827,8 @@
       <c r="B195" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C195" s="5">
-        <v>427.56890869140619</v>
+      <c r="C195">
+        <v>499.49</v>
       </c>
       <c r="D195">
         <v>373.82199096679688</v>
@@ -5841,8 +5841,8 @@
       <c r="B196" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C196" s="5">
-        <v>597.08477783203125</v>
+      <c r="C196">
+        <v>597.08000000000004</v>
       </c>
       <c r="D196">
         <v>458.5328369140625</v>
@@ -5855,8 +5855,8 @@
       <c r="B197" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C197" s="5">
-        <v>607.8558349609375</v>
+      <c r="C197">
+        <v>607.86</v>
       </c>
       <c r="D197">
         <v>503.07781982421881</v>
@@ -5869,7 +5869,7 @@
       <c r="B198" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C198" s="5">
+      <c r="C198">
         <v>53</v>
       </c>
     </row>
@@ -5880,8 +5880,8 @@
       <c r="B199" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C199" s="5">
-        <v>57.448986053466797</v>
+      <c r="C199">
+        <v>57.45</v>
       </c>
       <c r="D199">
         <v>51.823989868164062</v>
@@ -5894,8 +5894,8 @@
       <c r="B200" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C200" s="5">
-        <v>56.932968139648438</v>
+      <c r="C200">
+        <v>56.93</v>
       </c>
       <c r="D200">
         <v>51.047527313232422</v>
@@ -5908,8 +5908,8 @@
       <c r="B201" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C201" s="5">
-        <v>43.364948272705078</v>
+      <c r="C201">
+        <v>50</v>
       </c>
       <c r="D201">
         <v>39.569576263427727</v>
@@ -5922,8 +5922,8 @@
       <c r="B202" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C202" s="5">
-        <v>43.568576812744141</v>
+      <c r="C202">
+        <v>50.9</v>
       </c>
       <c r="D202">
         <v>40.316394805908203</v>
@@ -5936,8 +5936,8 @@
       <c r="B203" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C203" s="5">
-        <v>53.198196411132812</v>
+      <c r="C203">
+        <v>53.2</v>
       </c>
       <c r="D203">
         <v>44.968841552734382</v>
@@ -5950,8 +5950,8 @@
       <c r="B204" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C204" s="5">
-        <v>56.819843292236328</v>
+      <c r="C204">
+        <v>56.82</v>
       </c>
       <c r="D204">
         <v>49.489749908447273</v>
@@ -5964,7 +5964,7 @@
       <c r="B205" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C205" s="5">
+      <c r="C205">
         <v>140</v>
       </c>
     </row>
@@ -5975,8 +5975,8 @@
       <c r="B206" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="C206" s="5">
-        <v>139.7267150878906</v>
+      <c r="C206">
+        <v>139.72999999999999</v>
       </c>
       <c r="D206">
         <v>113.4280090332031</v>
@@ -5989,8 +5989,8 @@
       <c r="B207" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="C207" s="5">
-        <v>154.6648254394531</v>
+      <c r="C207">
+        <v>154.66</v>
       </c>
       <c r="D207">
         <v>127.60427093505859</v>
@@ -6003,8 +6003,8 @@
       <c r="B208" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="C208" s="5">
-        <v>110.2776565551758</v>
+      <c r="C208">
+        <v>127.15</v>
       </c>
       <c r="D208">
         <v>104.20326232910161</v>
@@ -6017,8 +6017,8 @@
       <c r="B209" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="C209" s="5">
-        <v>100.0591506958008</v>
+      <c r="C209">
+        <v>116.89</v>
       </c>
       <c r="D209">
         <v>96.440437316894531</v>
@@ -6031,8 +6031,8 @@
       <c r="B210" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="C210" s="5">
-        <v>142.53959655761719</v>
+      <c r="C210">
+        <v>142.54</v>
       </c>
       <c r="D210">
         <v>119.4929962158203</v>
@@ -6045,8 +6045,8 @@
       <c r="B211" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="C211" s="5">
-        <v>151.97724914550781</v>
+      <c r="C211">
+        <v>151.97999999999999</v>
       </c>
       <c r="D211">
         <v>131.572265625</v>
@@ -6059,7 +6059,7 @@
       <c r="B212" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C212" s="5">
+      <c r="C212">
         <v>382</v>
       </c>
     </row>
@@ -6070,8 +6070,8 @@
       <c r="B213" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C213" s="5">
-        <v>391.67355346679688</v>
+      <c r="C213">
+        <v>391.67</v>
       </c>
       <c r="D213">
         <v>301.41409301757812</v>
@@ -6084,8 +6084,8 @@
       <c r="B214" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C214" s="5">
-        <v>420.21514892578119</v>
+      <c r="C214">
+        <v>420.22</v>
       </c>
       <c r="D214">
         <v>350.73275756835938</v>
@@ -6098,8 +6098,8 @@
       <c r="B215" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C215" s="5">
-        <v>333.5904541015625</v>
+      <c r="C215">
+        <v>384.63</v>
       </c>
       <c r="D215">
         <v>294.98013305664062</v>
@@ -6112,8 +6112,8 @@
       <c r="B216" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C216" s="5">
-        <v>267.21804809570312</v>
+      <c r="C216">
+        <v>312.17</v>
       </c>
       <c r="D216">
         <v>251.1244812011719</v>
@@ -6126,8 +6126,8 @@
       <c r="B217" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C217" s="5">
-        <v>399.21829223632812</v>
+      <c r="C217">
+        <v>399.22</v>
       </c>
       <c r="D217">
         <v>308.05377197265619</v>
@@ -6140,8 +6140,8 @@
       <c r="B218" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C218" s="5">
-        <v>411.21258544921881</v>
+      <c r="C218">
+        <v>411.21</v>
       </c>
       <c r="D218">
         <v>346.18267822265619</v>
@@ -6154,7 +6154,7 @@
       <c r="B219" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C219" s="5">
+      <c r="C219">
         <v>357</v>
       </c>
     </row>
@@ -6165,8 +6165,8 @@
       <c r="B220" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="C220" s="5">
-        <v>373.22103881835938</v>
+      <c r="C220">
+        <v>373.22</v>
       </c>
       <c r="D220">
         <v>288.19009399414062</v>
@@ -6179,8 +6179,8 @@
       <c r="B221" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="C221" s="5">
-        <v>371.93951416015619</v>
+      <c r="C221">
+        <v>371.94</v>
       </c>
       <c r="D221">
         <v>323.42037963867188</v>
@@ -6193,8 +6193,8 @@
       <c r="B222" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="C222" s="5">
-        <v>250.22059631347659</v>
+      <c r="C222">
+        <v>288.51</v>
       </c>
       <c r="D222">
         <v>225.69671630859381</v>
@@ -6207,8 +6207,8 @@
       <c r="B223" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="C223" s="5">
-        <v>239.70887756347659</v>
+      <c r="C223">
+        <v>280.02999999999997</v>
       </c>
       <c r="D223">
         <v>226.0042419433594</v>
@@ -6221,8 +6221,8 @@
       <c r="B224" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="C224" s="5">
-        <v>379.87564086914062</v>
+      <c r="C224">
+        <v>379.88</v>
       </c>
       <c r="D224">
         <v>301.72601318359381</v>
@@ -6235,8 +6235,8 @@
       <c r="B225" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="C225" s="5">
-        <v>375.82174682617188</v>
+      <c r="C225">
+        <v>375.82</v>
       </c>
       <c r="D225">
         <v>318.5611572265625</v>
@@ -6249,7 +6249,7 @@
       <c r="B226" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C226" s="5">
+      <c r="C226">
         <v>140</v>
       </c>
     </row>
@@ -6260,8 +6260,8 @@
       <c r="B227" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C227" s="5">
-        <v>153.784912109375</v>
+      <c r="C227">
+        <v>153.78</v>
       </c>
       <c r="D227">
         <v>133.9944763183594</v>
@@ -6274,8 +6274,8 @@
       <c r="B228" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C228" s="5">
-        <v>155.3303527832031</v>
+      <c r="C228">
+        <v>155.33000000000001</v>
       </c>
       <c r="D228">
         <v>138.2807922363281</v>
@@ -6288,8 +6288,8 @@
       <c r="B229" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C229" s="5">
-        <v>127.5233459472656</v>
+      <c r="C229">
+        <v>147.04</v>
       </c>
       <c r="D229">
         <v>102.030647277832</v>
@@ -6302,8 +6302,8 @@
       <c r="B230" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C230" s="5">
-        <v>106.3494338989258</v>
+      <c r="C230">
+        <v>124.24</v>
       </c>
       <c r="D230">
         <v>95.039512634277344</v>
@@ -6316,8 +6316,8 @@
       <c r="B231" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C231" s="5">
-        <v>137.7015380859375</v>
+      <c r="C231">
+        <v>137.69999999999999</v>
       </c>
       <c r="D231">
         <v>109.7117156982422</v>
@@ -6330,8 +6330,8 @@
       <c r="B232" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C232" s="5">
-        <v>144.42631530761719</v>
+      <c r="C232">
+        <v>144.43</v>
       </c>
       <c r="D232">
         <v>127.9830703735352</v>
@@ -6344,7 +6344,7 @@
       <c r="B233" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C233" s="5">
+      <c r="C233">
         <v>579</v>
       </c>
     </row>
@@ -6355,8 +6355,8 @@
       <c r="B234" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C234" s="5">
-        <v>613.87066650390625</v>
+      <c r="C234">
+        <v>613.87</v>
       </c>
       <c r="D234">
         <v>425.54278564453119</v>
@@ -6369,8 +6369,8 @@
       <c r="B235" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C235" s="5">
-        <v>619.56756591796875</v>
+      <c r="C235">
+        <v>619.57000000000005</v>
       </c>
       <c r="D235">
         <v>446.9644775390625</v>
@@ -6383,8 +6383,8 @@
       <c r="B236" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C236" s="5">
-        <v>502.27276611328119</v>
+      <c r="C236">
+        <v>579.12</v>
       </c>
       <c r="D236">
         <v>384.98226928710938</v>
@@ -6397,8 +6397,8 @@
       <c r="B237" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C237" s="5">
-        <v>414.98855590820312</v>
+      <c r="C237">
+        <v>484.79</v>
       </c>
       <c r="D237">
         <v>350.948486328125</v>
@@ -6411,8 +6411,8 @@
       <c r="B238" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C238" s="5">
-        <v>631.2509765625</v>
+      <c r="C238">
+        <v>631.25</v>
       </c>
       <c r="D238">
         <v>419.2447509765625</v>
@@ -6425,8 +6425,8 @@
       <c r="B239" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C239" s="5">
-        <v>690.51190185546875</v>
+      <c r="C239">
+        <v>690.51</v>
       </c>
       <c r="D239">
         <v>464.8995361328125</v>
@@ -6439,7 +6439,7 @@
       <c r="B240" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C240" s="5">
+      <c r="C240">
         <v>525</v>
       </c>
     </row>
@@ -6450,8 +6450,8 @@
       <c r="B241" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="C241" s="5">
-        <v>560.0821533203125</v>
+      <c r="C241">
+        <v>560.08000000000004</v>
       </c>
       <c r="D241">
         <v>404.44195556640619</v>
@@ -6464,8 +6464,8 @@
       <c r="B242" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="C242" s="5">
-        <v>565.5467529296875</v>
+      <c r="C242">
+        <v>565.54999999999995</v>
       </c>
       <c r="D242">
         <v>435.29580688476562</v>
@@ -6478,8 +6478,8 @@
       <c r="B243" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="C243" s="5">
-        <v>401.14044189453119</v>
+      <c r="C243">
+        <v>462.52</v>
       </c>
       <c r="D243">
         <v>333.63177490234381</v>
@@ -6492,8 +6492,8 @@
       <c r="B244" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="C244" s="5">
-        <v>382.86672973632812</v>
+      <c r="C244">
+        <v>447.27</v>
       </c>
       <c r="D244">
         <v>329.340576171875</v>
@@ -6506,8 +6506,8 @@
       <c r="B245" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="C245" s="5">
-        <v>530.3734130859375</v>
+      <c r="C245">
+        <v>530.37</v>
       </c>
       <c r="D245">
         <v>408.98202514648438</v>
@@ -6520,8 +6520,8 @@
       <c r="B246" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="C246" s="5">
-        <v>571.094482421875</v>
+      <c r="C246">
+        <v>571.09</v>
       </c>
       <c r="D246">
         <v>456.42752075195312</v>
@@ -6534,7 +6534,7 @@
       <c r="B247" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C247" s="5">
+      <c r="C247">
         <v>238</v>
       </c>
     </row>
@@ -6545,8 +6545,8 @@
       <c r="B248" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C248" s="5">
-        <v>269.31732177734381</v>
+      <c r="C248">
+        <v>269.32</v>
       </c>
       <c r="D248">
         <v>198.57331848144531</v>
@@ -6559,8 +6559,8 @@
       <c r="B249" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C249" s="5">
-        <v>287.71942138671881</v>
+      <c r="C249">
+        <v>287.72000000000003</v>
       </c>
       <c r="D249">
         <v>224.24348449707031</v>
@@ -6573,8 +6573,8 @@
       <c r="B250" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C250" s="5">
-        <v>226.63270568847659</v>
+      <c r="C250">
+        <v>261.31</v>
       </c>
       <c r="D250">
         <v>195.2565612792969</v>
@@ -6587,8 +6587,8 @@
       <c r="B251" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C251" s="5">
-        <v>170.4305725097656</v>
+      <c r="C251">
+        <v>199.1</v>
       </c>
       <c r="D251">
         <v>151.54718017578119</v>
@@ -6601,8 +6601,8 @@
       <c r="B252" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C252" s="5">
-        <v>240.3313293457031</v>
+      <c r="C252">
+        <v>240.33</v>
       </c>
       <c r="D252">
         <v>183.90892028808591</v>
@@ -6615,8 +6615,8 @@
       <c r="B253" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C253" s="5">
-        <v>253.5285339355469</v>
+      <c r="C253">
+        <v>253.53</v>
       </c>
       <c r="D253">
         <v>204.8121643066406</v>
@@ -6629,7 +6629,7 @@
       <c r="B254" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C254" s="5">
+      <c r="C254">
         <v>672</v>
       </c>
     </row>
@@ -6640,8 +6640,8 @@
       <c r="B255" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C255" s="5">
-        <v>823.835693359375</v>
+      <c r="C255">
+        <v>823.84</v>
       </c>
       <c r="D255">
         <v>596.20733642578125</v>
@@ -6654,8 +6654,8 @@
       <c r="B256" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C256" s="5">
-        <v>796.06011962890625</v>
+      <c r="C256">
+        <v>796.06</v>
       </c>
       <c r="D256">
         <v>609.1470947265625</v>
@@ -6668,8 +6668,8 @@
       <c r="B257" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C257" s="5">
-        <v>576.672119140625</v>
+      <c r="C257">
+        <v>664.91</v>
       </c>
       <c r="D257">
         <v>490.48367309570312</v>
@@ -6682,8 +6682,8 @@
       <c r="B258" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C258" s="5">
-        <v>470.08309936523438</v>
+      <c r="C258">
+        <v>549.16</v>
       </c>
       <c r="D258">
         <v>414.6336669921875</v>
@@ -6696,8 +6696,8 @@
       <c r="B259" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C259" s="5">
-        <v>657.07373046875</v>
+      <c r="C259">
+        <v>657.07</v>
       </c>
       <c r="D259">
         <v>511.55938720703119</v>
@@ -6710,8 +6710,8 @@
       <c r="B260" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C260" s="5">
-        <v>772.15777587890625</v>
+      <c r="C260">
+        <v>772.16</v>
       </c>
       <c r="D260">
         <v>616.67767333984375</v>
@@ -6724,7 +6724,7 @@
       <c r="B261" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C261" s="5">
+      <c r="C261">
         <v>759</v>
       </c>
     </row>
@@ -6735,8 +6735,8 @@
       <c r="B262" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C262" s="5">
-        <v>775.49810791015625</v>
+      <c r="C262">
+        <v>775.5</v>
       </c>
       <c r="D262">
         <v>658.9708251953125</v>
@@ -6749,8 +6749,8 @@
       <c r="B263" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C263" s="5">
-        <v>782.52880859375</v>
+      <c r="C263">
+        <v>782.53</v>
       </c>
       <c r="D263">
         <v>679.638427734375</v>
@@ -6763,8 +6763,8 @@
       <c r="B264" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C264" s="5">
-        <v>678.27313232421875</v>
+      <c r="C264">
+        <v>782.05</v>
       </c>
       <c r="D264">
         <v>589.46954345703125</v>
@@ -6777,8 +6777,8 @@
       <c r="B265" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C265" s="5">
-        <v>607.060546875</v>
+      <c r="C265">
+        <v>709.17</v>
       </c>
       <c r="D265">
         <v>540.9990234375</v>
@@ -6791,8 +6791,8 @@
       <c r="B266" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C266" s="5">
-        <v>748.86993408203125</v>
+      <c r="C266">
+        <v>748.87</v>
       </c>
       <c r="D266">
         <v>664.89630126953125</v>
@@ -6805,8 +6805,8 @@
       <c r="B267" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C267" s="5">
-        <v>787.48626708984375</v>
+      <c r="C267">
+        <v>787.49</v>
       </c>
       <c r="D267">
         <v>734.254638671875</v>
@@ -6819,7 +6819,7 @@
       <c r="B268" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C268" s="5">
+      <c r="C268">
         <v>487</v>
       </c>
     </row>
@@ -6830,8 +6830,8 @@
       <c r="B269" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C269" s="5">
-        <v>503.85983276367188</v>
+      <c r="C269">
+        <v>503.86</v>
       </c>
       <c r="D269">
         <v>410.311767578125</v>
@@ -6844,8 +6844,8 @@
       <c r="B270" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C270" s="5">
-        <v>537.20880126953125</v>
+      <c r="C270">
+        <v>537.21</v>
       </c>
       <c r="D270">
         <v>453.6417236328125</v>
@@ -6858,8 +6858,8 @@
       <c r="B271" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C271" s="5">
-        <v>409.7467041015625</v>
+      <c r="C271">
+        <v>472.44</v>
       </c>
       <c r="D271">
         <v>353.86737060546881</v>
@@ -6872,8 +6872,8 @@
       <c r="B272" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C272" s="5">
-        <v>356.12167358398438</v>
+      <c r="C272">
+        <v>416.02</v>
       </c>
       <c r="D272">
         <v>317.90692138671881</v>
@@ -6886,8 +6886,8 @@
       <c r="B273" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C273" s="5">
-        <v>456.69741821289062</v>
+      <c r="C273">
+        <v>456.7</v>
       </c>
       <c r="D273">
         <v>376.06600952148438</v>
@@ -6900,8 +6900,8 @@
       <c r="B274" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C274" s="5">
-        <v>505.51638793945312</v>
+      <c r="C274">
+        <v>505.52</v>
       </c>
       <c r="D274">
         <v>451.37997436523438</v>
@@ -6914,7 +6914,7 @@
       <c r="B275" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C275" s="5">
+      <c r="C275">
         <v>394</v>
       </c>
     </row>
@@ -6925,8 +6925,8 @@
       <c r="B276" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C276" s="5">
-        <v>433.86807250976562</v>
+      <c r="C276">
+        <v>433.87</v>
       </c>
       <c r="D276">
         <v>344.56292724609381</v>
@@ -6939,8 +6939,8 @@
       <c r="B277" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C277" s="5">
-        <v>424.15670776367188</v>
+      <c r="C277">
+        <v>424.16</v>
       </c>
       <c r="D277">
         <v>349.958740234375</v>
@@ -6953,8 +6953,8 @@
       <c r="B278" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C278" s="5">
-        <v>328.26947021484381</v>
+      <c r="C278">
+        <v>378.5</v>
       </c>
       <c r="D278">
         <v>264.00625610351562</v>
@@ -6967,8 +6967,8 @@
       <c r="B279" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C279" s="5">
-        <v>286.76156616210938</v>
+      <c r="C279">
+        <v>335</v>
       </c>
       <c r="D279">
         <v>243.35601806640619</v>
@@ -6981,8 +6981,8 @@
       <c r="B280" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C280" s="5">
-        <v>402.34628295898438</v>
+      <c r="C280">
+        <v>402.35</v>
       </c>
       <c r="D280">
         <v>296.45669555664062</v>
@@ -6995,8 +6995,8 @@
       <c r="B281" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C281" s="5">
-        <v>426.72879028320312</v>
+      <c r="C281">
+        <v>426.73</v>
       </c>
       <c r="D281">
         <v>362.71630859375</v>
@@ -7009,7 +7009,7 @@
       <c r="B282" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C282" s="5">
+      <c r="C282">
         <v>287</v>
       </c>
     </row>
@@ -7020,8 +7020,8 @@
       <c r="B283" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C283" s="5">
-        <v>282.777099609375</v>
+      <c r="C283">
+        <v>282.77999999999997</v>
       </c>
       <c r="D283">
         <v>230.8039245605469</v>
@@ -7034,8 +7034,8 @@
       <c r="B284" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C284" s="5">
-        <v>300.24514770507812</v>
+      <c r="C284">
+        <v>300.25</v>
       </c>
       <c r="D284">
         <v>250.45957946777341</v>
@@ -7048,8 +7048,8 @@
       <c r="B285" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C285" s="5">
-        <v>227.54325866699219</v>
+      <c r="C285">
+        <v>262.36</v>
       </c>
       <c r="D285">
         <v>190.74848937988281</v>
@@ -7062,8 +7062,8 @@
       <c r="B286" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C286" s="5">
-        <v>184.95831298828119</v>
+      <c r="C286">
+        <v>216.07</v>
       </c>
       <c r="D286">
         <v>165.83294677734381</v>
@@ -7076,8 +7076,8 @@
       <c r="B287" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C287" s="5">
-        <v>267.40802001953119</v>
+      <c r="C287">
+        <v>267.41000000000003</v>
       </c>
       <c r="D287">
         <v>218.79786682128909</v>
@@ -7090,8 +7090,8 @@
       <c r="B288" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C288" s="5">
-        <v>276.45388793945312</v>
+      <c r="C288">
+        <v>276.45</v>
       </c>
       <c r="D288">
         <v>240.8728942871094</v>
@@ -7104,7 +7104,7 @@
       <c r="B289" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C289" s="5">
+      <c r="C289">
         <v>437</v>
       </c>
     </row>
@@ -7115,8 +7115,8 @@
       <c r="B290" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C290" s="5">
-        <v>448.737060546875</v>
+      <c r="C290">
+        <v>448.74</v>
       </c>
       <c r="D290">
         <v>343.45904541015619</v>
@@ -7129,8 +7129,8 @@
       <c r="B291" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C291" s="5">
-        <v>451.71661376953119</v>
+      <c r="C291">
+        <v>451.72</v>
       </c>
       <c r="D291">
         <v>367.12744140625</v>
@@ -7143,8 +7143,8 @@
       <c r="B292" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C292" s="5">
-        <v>376.39678955078119</v>
+      <c r="C292">
+        <v>433.99</v>
       </c>
       <c r="D292">
         <v>327.27645874023438</v>
@@ -7157,8 +7157,8 @@
       <c r="B293" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C293" s="5">
-        <v>294.16156005859381</v>
+      <c r="C293">
+        <v>343.64</v>
       </c>
       <c r="D293">
         <v>262.60540771484381</v>
@@ -7171,8 +7171,8 @@
       <c r="B294" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C294" s="5">
-        <v>437.58151245117188</v>
+      <c r="C294">
+        <v>437.58</v>
       </c>
       <c r="D294">
         <v>334.991455078125</v>
@@ -7185,8 +7185,8 @@
       <c r="B295" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C295" s="5">
-        <v>536.66168212890625</v>
+      <c r="C295">
+        <v>536.66</v>
       </c>
       <c r="D295">
         <v>406.6793212890625</v>
@@ -7199,7 +7199,7 @@
       <c r="B296" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C296" s="5">
+      <c r="C296">
         <v>255</v>
       </c>
     </row>
@@ -7210,8 +7210,8 @@
       <c r="B297" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C297" s="5">
-        <v>271.89041137695312</v>
+      <c r="C297">
+        <v>271.89</v>
       </c>
       <c r="D297">
         <v>219.6317138671875</v>
@@ -7224,8 +7224,8 @@
       <c r="B298" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C298" s="5">
-        <v>261.67578125</v>
+      <c r="C298">
+        <v>261.68</v>
       </c>
       <c r="D298">
         <v>218.3518371582031</v>
@@ -7238,8 +7238,8 @@
       <c r="B299" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C299" s="5">
-        <v>211.1293640136719</v>
+      <c r="C299">
+        <v>243.43</v>
       </c>
       <c r="D299">
         <v>173.37117004394531</v>
@@ -7252,8 +7252,8 @@
       <c r="B300" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C300" s="5">
-        <v>160.53364562988281</v>
+      <c r="C300">
+        <v>187.54</v>
       </c>
       <c r="D300">
         <v>136.33711242675781</v>
@@ -7266,8 +7266,8 @@
       <c r="B301" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C301" s="5">
-        <v>242.17713928222659</v>
+      <c r="C301">
+        <v>242.18</v>
       </c>
       <c r="D301">
         <v>176.7649841308594</v>
@@ -7280,8 +7280,8 @@
       <c r="B302" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C302" s="5">
-        <v>247.33558654785159</v>
+      <c r="C302">
+        <v>247.34</v>
       </c>
       <c r="D302">
         <v>207.10072326660159</v>
@@ -7294,7 +7294,7 @@
       <c r="B303" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C303" s="5">
+      <c r="C303">
         <v>480</v>
       </c>
     </row>
@@ -7305,8 +7305,8 @@
       <c r="B304" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C304" s="5">
-        <v>517.66510009765625</v>
+      <c r="C304">
+        <v>517.66999999999996</v>
       </c>
       <c r="D304">
         <v>402.2755126953125</v>
@@ -7319,8 +7319,8 @@
       <c r="B305" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C305" s="5">
-        <v>520.71881103515625</v>
+      <c r="C305">
+        <v>520.72</v>
       </c>
       <c r="D305">
         <v>425.51553344726562</v>
@@ -7333,8 +7333,8 @@
       <c r="B306" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C306" s="5">
-        <v>410.85757446289062</v>
+      <c r="C306">
+        <v>473.72</v>
       </c>
       <c r="D306">
         <v>351.53350830078119</v>
@@ -7347,8 +7347,8 @@
       <c r="B307" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C307" s="5">
-        <v>342.0443115234375</v>
+      <c r="C307">
+        <v>399.58</v>
       </c>
       <c r="D307">
         <v>306.72927856445312</v>
@@ -7361,8 +7361,8 @@
       <c r="B308" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C308" s="5">
-        <v>465.7445068359375</v>
+      <c r="C308">
+        <v>465.74</v>
       </c>
       <c r="D308">
         <v>370.2054443359375</v>
@@ -7375,8 +7375,8 @@
       <c r="B309" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C309" s="5">
-        <v>481.32949829101562</v>
+      <c r="C309">
+        <v>481.33</v>
       </c>
       <c r="D309">
         <v>403.42938232421881</v>
@@ -7389,7 +7389,7 @@
       <c r="B310" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C310" s="5">
+      <c r="C310">
         <v>504</v>
       </c>
     </row>
@@ -7400,8 +7400,8 @@
       <c r="B311" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C311" s="5">
-        <v>515.85638427734375</v>
+      <c r="C311">
+        <v>515.86</v>
       </c>
       <c r="D311">
         <v>409.27984619140619</v>
@@ -7414,8 +7414,8 @@
       <c r="B312" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C312" s="5">
-        <v>570.31781005859375</v>
+      <c r="C312">
+        <v>570.32000000000005</v>
       </c>
       <c r="D312">
         <v>466.29522705078119</v>
@@ -7428,8 +7428,8 @@
       <c r="B313" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C313" s="5">
-        <v>445.86553955078119</v>
+      <c r="C313">
+        <v>514.09</v>
       </c>
       <c r="D313">
         <v>388.69036865234381</v>
@@ -7442,8 +7442,8 @@
       <c r="B314" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C314" s="5">
-        <v>354.0518798828125</v>
+      <c r="C314">
+        <v>413.61</v>
       </c>
       <c r="D314">
         <v>313.19589233398438</v>
@@ -7456,8 +7456,8 @@
       <c r="B315" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C315" s="5">
-        <v>455.50863647460938</v>
+      <c r="C315">
+        <v>455.51</v>
       </c>
       <c r="D315">
         <v>376.29351806640619</v>
@@ -7470,8 +7470,8 @@
       <c r="B316" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C316" s="5">
-        <v>557.63946533203125</v>
+      <c r="C316">
+        <v>557.64</v>
       </c>
       <c r="D316">
         <v>455.36825561523438</v>
@@ -7484,7 +7484,7 @@
       <c r="B317" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C317" s="5">
+      <c r="C317">
         <v>546</v>
       </c>
     </row>
@@ -7495,8 +7495,8 @@
       <c r="B318" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C318" s="5">
-        <v>478.61679077148438</v>
+      <c r="C318">
+        <v>478.62</v>
       </c>
       <c r="D318">
         <v>354.32589721679688</v>
@@ -7509,8 +7509,8 @@
       <c r="B319" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C319" s="5">
-        <v>478.8997802734375</v>
+      <c r="C319">
+        <v>478.9</v>
       </c>
       <c r="D319">
         <v>357.88372802734381</v>
@@ -7523,8 +7523,8 @@
       <c r="B320" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C320" s="5">
-        <v>409.98672485351562</v>
+      <c r="C320">
+        <v>472.72</v>
       </c>
       <c r="D320">
         <v>334.069580078125</v>
@@ -7537,8 +7537,8 @@
       <c r="B321" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C321" s="5">
-        <v>349.06973266601562</v>
+      <c r="C321">
+        <v>407.79</v>
       </c>
       <c r="D321">
         <v>308.25350952148438</v>
@@ -7551,8 +7551,8 @@
       <c r="B322" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C322" s="5">
-        <v>504.03561401367188</v>
+      <c r="C322">
+        <v>504.04</v>
       </c>
       <c r="D322">
         <v>360.69366455078119</v>
@@ -7565,8 +7565,8 @@
       <c r="B323" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C323" s="5">
-        <v>523.78143310546875</v>
+      <c r="C323">
+        <v>523.78</v>
       </c>
       <c r="D323">
         <v>395.55691528320312</v>
@@ -7579,7 +7579,7 @@
       <c r="B324" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C324" s="5">
+      <c r="C324">
         <v>395</v>
       </c>
     </row>
@@ -7590,8 +7590,8 @@
       <c r="B325" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C325" s="5">
-        <v>390.630859375</v>
+      <c r="C325">
+        <v>390.63</v>
       </c>
       <c r="D325">
         <v>315.308837890625</v>
@@ -7604,8 +7604,8 @@
       <c r="B326" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C326" s="5">
-        <v>401.23672485351562</v>
+      <c r="C326">
+        <v>401.24</v>
       </c>
       <c r="D326">
         <v>332.75897216796881</v>
@@ -7618,8 +7618,8 @@
       <c r="B327" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C327" s="5">
-        <v>309.97430419921881</v>
+      <c r="C327">
+        <v>357.4</v>
       </c>
       <c r="D327">
         <v>273.93368530273438</v>
@@ -7632,8 +7632,8 @@
       <c r="B328" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C328" s="5">
-        <v>299.77752685546881</v>
+      <c r="C328">
+        <v>350.2</v>
       </c>
       <c r="D328">
         <v>261.09597778320312</v>
@@ -7646,8 +7646,8 @@
       <c r="B329" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C329" s="5">
-        <v>371.67803955078119</v>
+      <c r="C329">
+        <v>371.68</v>
       </c>
       <c r="D329">
         <v>293.78390502929688</v>
@@ -7660,8 +7660,8 @@
       <c r="B330" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C330" s="5">
-        <v>388.09121704101562</v>
+      <c r="C330">
+        <v>388.09</v>
       </c>
       <c r="D330">
         <v>320.06195068359381</v>
@@ -7674,7 +7674,7 @@
       <c r="B331" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C331" s="5">
+      <c r="C331">
         <v>464</v>
       </c>
     </row>
@@ -7685,8 +7685,8 @@
       <c r="B332" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C332" s="5">
-        <v>462.4915771484375</v>
+      <c r="C332">
+        <v>462.49</v>
       </c>
       <c r="D332">
         <v>303.42880249023438</v>
@@ -7699,8 +7699,8 @@
       <c r="B333" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C333" s="5">
-        <v>455.87014770507812</v>
+      <c r="C333">
+        <v>455.87</v>
       </c>
       <c r="D333">
         <v>320.703125</v>
@@ -7713,8 +7713,8 @@
       <c r="B334" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C334" s="5">
-        <v>364.77871704101562</v>
+      <c r="C334">
+        <v>420.59</v>
       </c>
       <c r="D334">
         <v>271.99179077148438</v>
@@ -7727,8 +7727,8 @@
       <c r="B335" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C335" s="5">
-        <v>317.21530151367188</v>
+      <c r="C335">
+        <v>370.57</v>
       </c>
       <c r="D335">
         <v>250.96788024902341</v>
@@ -7741,8 +7741,8 @@
       <c r="B336" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C336" s="5">
-        <v>467.89804077148438</v>
+      <c r="C336">
+        <v>467.9</v>
       </c>
       <c r="D336">
         <v>282.16842651367188</v>
@@ -7755,8 +7755,8 @@
       <c r="B337" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C337" s="5">
-        <v>517.28460693359375</v>
+      <c r="C337">
+        <v>517.28</v>
       </c>
       <c r="D337">
         <v>332.83233642578119</v>
@@ -7769,7 +7769,7 @@
       <c r="B338" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C338" s="5">
+      <c r="C338">
         <v>357</v>
       </c>
     </row>
@@ -7780,8 +7780,8 @@
       <c r="B339" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C339" s="5">
-        <v>365.99029541015619</v>
+      <c r="C339">
+        <v>365.99</v>
       </c>
       <c r="D339">
         <v>268.7884521484375</v>
@@ -7794,8 +7794,8 @@
       <c r="B340" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C340" s="5">
-        <v>383.64031982421881</v>
+      <c r="C340">
+        <v>383.64</v>
       </c>
       <c r="D340">
         <v>272.62661743164062</v>
@@ -7808,8 +7808,8 @@
       <c r="B341" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C341" s="5">
-        <v>291.47982788085938</v>
+      <c r="C341">
+        <v>336.08</v>
       </c>
       <c r="D341">
         <v>236.6294860839844</v>
@@ -7822,8 +7822,8 @@
       <c r="B342" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C342" s="5">
-        <v>230.5319519042969</v>
+      <c r="C342">
+        <v>269.31</v>
       </c>
       <c r="D342">
         <v>192.8927001953125</v>
@@ -7836,8 +7836,8 @@
       <c r="B343" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C343" s="5">
-        <v>352.72265625</v>
+      <c r="C343">
+        <v>352.72</v>
       </c>
       <c r="D343">
         <v>249.6482849121094</v>
@@ -7850,8 +7850,8 @@
       <c r="B344" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C344" s="5">
-        <v>390.161865234375</v>
+      <c r="C344">
+        <v>390.16</v>
       </c>
       <c r="D344">
         <v>290.67526245117188</v>
@@ -7864,7 +7864,7 @@
       <c r="B345" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C345" s="5">
+      <c r="C345">
         <v>529</v>
       </c>
     </row>
@@ -7875,8 +7875,8 @@
       <c r="B346" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C346" s="5">
-        <v>497.02578735351562</v>
+      <c r="C346">
+        <v>497.03</v>
       </c>
       <c r="D346">
         <v>392.79617309570312</v>
@@ -7889,8 +7889,8 @@
       <c r="B347" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C347" s="5">
-        <v>513.4305419921875</v>
+      <c r="C347">
+        <v>513.42999999999995</v>
       </c>
       <c r="D347">
         <v>407.69143676757812</v>
@@ -7903,8 +7903,8 @@
       <c r="B348" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C348" s="5">
-        <v>440.06820678710938</v>
+      <c r="C348">
+        <v>507.4</v>
       </c>
       <c r="D348">
         <v>354.23138427734381</v>
@@ -7917,8 +7917,8 @@
       <c r="B349" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C349" s="5">
-        <v>360.21194458007812</v>
+      <c r="C349">
+        <v>420.8</v>
       </c>
       <c r="D349">
         <v>296.928955078125</v>
@@ -7931,8 +7931,8 @@
       <c r="B350" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C350" s="5">
-        <v>484.36572265625</v>
+      <c r="C350">
+        <v>484.37</v>
       </c>
       <c r="D350">
         <v>355.7445068359375</v>
@@ -7945,8 +7945,8 @@
       <c r="B351" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C351" s="5">
-        <v>522.5037841796875</v>
+      <c r="C351">
+        <v>522.5</v>
       </c>
       <c r="D351">
         <v>404.91452026367188</v>
@@ -7959,7 +7959,7 @@
       <c r="B352" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C352" s="5">
+      <c r="C352">
         <v>822</v>
       </c>
     </row>
@@ -7970,8 +7970,8 @@
       <c r="B353" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C353" s="5">
-        <v>836.0531005859375</v>
+      <c r="C353">
+        <v>836.05</v>
       </c>
       <c r="D353">
         <v>596.49249267578125</v>
@@ -7984,8 +7984,8 @@
       <c r="B354" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C354" s="5">
-        <v>803.44927978515625</v>
+      <c r="C354">
+        <v>803.45</v>
       </c>
       <c r="D354">
         <v>608.41204833984375</v>
@@ -7998,8 +7998,8 @@
       <c r="B355" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C355" s="5">
-        <v>661.9969482421875</v>
+      <c r="C355">
+        <v>763.29</v>
       </c>
       <c r="D355">
         <v>573.05596923828125</v>
@@ -8012,8 +8012,8 @@
       <c r="B356" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C356" s="5">
-        <v>568.1314697265625</v>
+      <c r="C356">
+        <v>663.7</v>
       </c>
       <c r="D356">
         <v>471.344970703125</v>
@@ -8026,8 +8026,8 @@
       <c r="B357" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C357" s="5">
-        <v>776.66497802734375</v>
+      <c r="C357">
+        <v>776.66</v>
       </c>
       <c r="D357">
         <v>562.22821044921875</v>
@@ -8040,8 +8040,8 @@
       <c r="B358" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C358" s="5">
-        <v>860.67669677734375</v>
+      <c r="C358">
+        <v>860.68</v>
       </c>
       <c r="D358">
         <v>637.5743408203125</v>
@@ -8054,7 +8054,7 @@
       <c r="B359" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C359" s="5">
+      <c r="C359">
         <v>359</v>
       </c>
     </row>
@@ -8065,8 +8065,8 @@
       <c r="B360" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C360" s="5">
-        <v>375.40509033203119</v>
+      <c r="C360">
+        <v>375.41</v>
       </c>
       <c r="D360">
         <v>278.9991455078125</v>
@@ -8079,8 +8079,8 @@
       <c r="B361" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C361" s="5">
-        <v>373.12469482421881</v>
+      <c r="C361">
+        <v>373.12</v>
       </c>
       <c r="D361">
         <v>285.91867065429688</v>
@@ -8093,8 +8093,8 @@
       <c r="B362" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C362" s="5">
-        <v>313.55868530273438</v>
+      <c r="C362">
+        <v>361.54</v>
       </c>
       <c r="D362">
         <v>233.89909362792969</v>
@@ -8107,8 +8107,8 @@
       <c r="B363" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C363" s="5">
-        <v>269.35830688476562</v>
+      <c r="C363">
+        <v>314.67</v>
       </c>
       <c r="D363">
         <v>220.27534484863281</v>
@@ -8121,8 +8121,8 @@
       <c r="B364" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C364" s="5">
-        <v>371.28460693359381</v>
+      <c r="C364">
+        <v>371.28</v>
       </c>
       <c r="D364">
         <v>275.34121704101562</v>
@@ -8135,8 +8135,8 @@
       <c r="B365" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C365" s="5">
-        <v>372.9752197265625</v>
+      <c r="C365">
+        <v>372.98</v>
       </c>
       <c r="D365">
         <v>306.31881713867188</v>
@@ -8149,7 +8149,7 @@
       <c r="B366" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C366" s="5">
+      <c r="C366">
         <v>601</v>
       </c>
     </row>
@@ -8160,8 +8160,8 @@
       <c r="B367" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C367" s="5">
-        <v>576.18475341796875</v>
+      <c r="C367">
+        <v>576.17999999999995</v>
       </c>
       <c r="D367">
         <v>491.4898681640625</v>
@@ -8174,8 +8174,8 @@
       <c r="B368" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C368" s="5">
-        <v>578.06951904296875</v>
+      <c r="C368">
+        <v>578.07000000000005</v>
       </c>
       <c r="D368">
         <v>519.74945068359375</v>
@@ -8188,8 +8188,8 @@
       <c r="B369" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C369" s="5">
-        <v>440.6263427734375</v>
+      <c r="C369">
+        <v>508.05</v>
       </c>
       <c r="D369">
         <v>377.86810302734381</v>
@@ -8202,8 +8202,8 @@
       <c r="B370" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C370" s="5">
-        <v>394.17404174804688</v>
+      <c r="C370">
+        <v>460.48</v>
       </c>
       <c r="D370">
         <v>324.33419799804688</v>
@@ -8216,8 +8216,8 @@
       <c r="B371" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C371" s="5">
-        <v>511.39712524414062</v>
+      <c r="C371">
+        <v>511.4</v>
       </c>
       <c r="D371">
         <v>384.40719604492188</v>
@@ -8230,8 +8230,8 @@
       <c r="B372" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C372" s="5">
-        <v>579.98291015625</v>
+      <c r="C372">
+        <v>579.98</v>
       </c>
       <c r="D372">
         <v>494.397705078125</v>
@@ -8244,7 +8244,7 @@
       <c r="B373" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C373" s="5">
+      <c r="C373">
         <v>223</v>
       </c>
     </row>
@@ -8255,8 +8255,8 @@
       <c r="B374" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C374" s="5">
-        <v>254.01570129394531</v>
+      <c r="C374">
+        <v>254.02</v>
       </c>
       <c r="D374">
         <v>194.20610046386719</v>
@@ -8269,8 +8269,8 @@
       <c r="B375" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C375" s="5">
-        <v>259.42922973632812</v>
+      <c r="C375">
+        <v>259.43</v>
       </c>
       <c r="D375">
         <v>189.8313293457031</v>
@@ -8283,8 +8283,8 @@
       <c r="B376" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C376" s="5">
-        <v>185.23561096191409</v>
+      <c r="C376">
+        <v>213.58</v>
       </c>
       <c r="D376">
         <v>156.4908142089844</v>
@@ -8297,8 +8297,8 @@
       <c r="B377" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C377" s="5">
-        <v>184.8996276855469</v>
+      <c r="C377">
+        <v>216</v>
       </c>
       <c r="D377">
         <v>151.04182434082031</v>
@@ -8311,8 +8311,8 @@
       <c r="B378" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C378" s="5">
-        <v>256.96896362304688</v>
+      <c r="C378">
+        <v>256.97000000000003</v>
       </c>
       <c r="D378">
         <v>186.3009338378906</v>
@@ -8325,8 +8325,8 @@
       <c r="B379" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C379" s="5">
-        <v>265.5950927734375</v>
+      <c r="C379">
+        <v>265.60000000000002</v>
       </c>
       <c r="D379">
         <v>187.43342590332031</v>
@@ -8339,7 +8339,7 @@
       <c r="B380" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C380" s="5">
+      <c r="C380">
         <v>455</v>
       </c>
     </row>
@@ -8350,8 +8350,8 @@
       <c r="B381" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C381" s="5">
-        <v>461.47979736328119</v>
+      <c r="C381">
+        <v>461.48</v>
       </c>
       <c r="D381">
         <v>338.57080078125</v>
@@ -8364,8 +8364,8 @@
       <c r="B382" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C382" s="5">
-        <v>471.44049072265619</v>
+      <c r="C382">
+        <v>471.44</v>
       </c>
       <c r="D382">
         <v>366.95913696289062</v>
@@ -8378,8 +8378,8 @@
       <c r="B383" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C383" s="5">
-        <v>423.21829223632812</v>
+      <c r="C383">
+        <v>487.97</v>
       </c>
       <c r="D383">
         <v>365.46673583984381</v>
@@ -8392,8 +8392,8 @@
       <c r="B384" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C384" s="5">
-        <v>374.66976928710938</v>
+      <c r="C384">
+        <v>437.69</v>
       </c>
       <c r="D384">
         <v>307.8790283203125</v>
@@ -8406,8 +8406,8 @@
       <c r="B385" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C385" s="5">
-        <v>452.33419799804688</v>
+      <c r="C385">
+        <v>452.33</v>
       </c>
       <c r="D385">
         <v>380.47271728515619</v>
@@ -8420,8 +8420,8 @@
       <c r="B386" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C386" s="5">
-        <v>462.08798217773438</v>
+      <c r="C386">
+        <v>462.09</v>
       </c>
       <c r="D386">
         <v>373.938720703125</v>
@@ -8434,7 +8434,7 @@
       <c r="B387" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C387" s="5">
+      <c r="C387">
         <v>171</v>
       </c>
     </row>
@@ -8445,8 +8445,8 @@
       <c r="B388" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C388" s="5">
-        <v>199.2677001953125</v>
+      <c r="C388">
+        <v>199.27</v>
       </c>
       <c r="D388">
         <v>150.31141662597659</v>
@@ -8459,8 +8459,8 @@
       <c r="B389" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C389" s="5">
-        <v>200.22224426269531</v>
+      <c r="C389">
+        <v>200.22</v>
       </c>
       <c r="D389">
         <v>147.91242980957031</v>
@@ -8473,8 +8473,8 @@
       <c r="B390" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C390" s="5">
-        <v>138.66539001464841</v>
+      <c r="C390">
+        <v>159.88</v>
       </c>
       <c r="D390">
         <v>114.9441375732422</v>
@@ -8487,8 +8487,8 @@
       <c r="B391" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C391" s="5">
-        <v>120.85666656494141</v>
+      <c r="C391">
+        <v>141.19</v>
       </c>
       <c r="D391">
         <v>98.3463134765625</v>
@@ -8501,8 +8501,8 @@
       <c r="B392" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C392" s="5">
-        <v>184.2698974609375</v>
+      <c r="C392">
+        <v>184.27</v>
       </c>
       <c r="D392">
         <v>138.90582275390619</v>
@@ -8515,8 +8515,8 @@
       <c r="B393" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C393" s="5">
-        <v>194.4739990234375</v>
+      <c r="C393">
+        <v>194.47</v>
       </c>
       <c r="D393">
         <v>147.012939453125</v>
@@ -8529,7 +8529,7 @@
       <c r="B394" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C394" s="5">
+      <c r="C394">
         <v>184</v>
       </c>
     </row>
@@ -8540,8 +8540,8 @@
       <c r="B395" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C395" s="5">
-        <v>194.92041015625</v>
+      <c r="C395">
+        <v>194.92</v>
       </c>
       <c r="D395">
         <v>152.88188171386719</v>
@@ -8554,8 +8554,8 @@
       <c r="B396" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C396" s="5">
-        <v>192.3370056152344</v>
+      <c r="C396">
+        <v>192.34</v>
       </c>
       <c r="D396">
         <v>148.93443298339841</v>
@@ -8568,8 +8568,8 @@
       <c r="B397" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C397" s="5">
-        <v>156.29058837890619</v>
+      <c r="C397">
+        <v>180.2</v>
       </c>
       <c r="D397">
         <v>118.3282928466797</v>
@@ -8582,8 +8582,8 @@
       <c r="B398" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C398" s="5">
-        <v>106.9840927124023</v>
+      <c r="C398">
+        <v>124.98</v>
       </c>
       <c r="D398">
         <v>87.536308288574219</v>
@@ -8596,8 +8596,8 @@
       <c r="B399" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C399" s="5">
-        <v>175.53179931640619</v>
+      <c r="C399">
+        <v>175.53</v>
       </c>
       <c r="D399">
         <v>114.1182403564453</v>
@@ -8610,8 +8610,8 @@
       <c r="B400" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C400" s="5">
-        <v>187.83720397949219</v>
+      <c r="C400">
+        <v>187.84</v>
       </c>
       <c r="D400">
         <v>146.74583435058591</v>
@@ -8624,7 +8624,7 @@
       <c r="B401" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C401" s="5">
+      <c r="C401">
         <v>427</v>
       </c>
     </row>
@@ -8635,8 +8635,8 @@
       <c r="B402" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C402" s="5">
-        <v>411.45541381835938</v>
+      <c r="C402">
+        <v>411.46</v>
       </c>
       <c r="D402">
         <v>343.78128051757812</v>
@@ -8649,8 +8649,8 @@
       <c r="B403" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C403" s="5">
-        <v>424.59765625</v>
+      <c r="C403">
+        <v>424.6</v>
       </c>
       <c r="D403">
         <v>372.60379028320312</v>
@@ -8663,8 +8663,8 @@
       <c r="B404" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C404" s="5">
-        <v>316.84271240234381</v>
+      <c r="C404">
+        <v>365.32</v>
       </c>
       <c r="D404">
         <v>286.26828002929688</v>
@@ -8677,8 +8677,8 @@
       <c r="B405" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C405" s="5">
-        <v>293.89370727539062</v>
+      <c r="C405">
+        <v>343.33</v>
       </c>
       <c r="D405">
         <v>271.10247802734381</v>
@@ -8691,8 +8691,8 @@
       <c r="B406" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C406" s="5">
-        <v>379.1466064453125</v>
+      <c r="C406">
+        <v>379.15</v>
       </c>
       <c r="D406">
         <v>318.96673583984381</v>
@@ -8705,8 +8705,8 @@
       <c r="B407" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C407" s="5">
-        <v>427.06973266601562</v>
+      <c r="C407">
+        <v>427.07</v>
       </c>
       <c r="D407">
         <v>380.54220581054688</v>
@@ -8719,7 +8719,7 @@
       <c r="B408" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C408" s="5">
+      <c r="C408">
         <v>117</v>
       </c>
       <c r="D408">
@@ -8733,7 +8733,7 @@
       <c r="B409" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C409" s="5">
+      <c r="C409">
         <v>120</v>
       </c>
       <c r="D409">
@@ -8747,7 +8747,7 @@
       <c r="B410" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C410" s="5">
+      <c r="C410">
         <v>115</v>
       </c>
       <c r="D410">
@@ -8761,8 +8761,8 @@
       <c r="B411" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C411" s="5">
-        <v>91</v>
+      <c r="C411">
+        <v>104.92</v>
       </c>
       <c r="D411">
         <v>0</v>
@@ -8775,8 +8775,8 @@
       <c r="B412" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C412" s="5">
-        <v>77</v>
+      <c r="C412">
+        <v>89.95</v>
       </c>
       <c r="D412">
         <v>0</v>
@@ -8789,7 +8789,7 @@
       <c r="B413" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C413" s="5">
+      <c r="C413">
         <v>106</v>
       </c>
       <c r="D413">
@@ -8803,7 +8803,7 @@
       <c r="B414" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C414" s="5">
+      <c r="C414">
         <v>110</v>
       </c>
       <c r="D414">
@@ -8817,7 +8817,7 @@
       <c r="B415" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C415" s="5">
+      <c r="C415">
         <v>219</v>
       </c>
     </row>
@@ -8828,8 +8828,8 @@
       <c r="B416" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="C416" s="5">
-        <v>220.0609436035156</v>
+      <c r="C416">
+        <v>220.06</v>
       </c>
       <c r="D416">
         <v>172.68988037109381</v>
@@ -8842,8 +8842,8 @@
       <c r="B417" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="C417" s="5">
-        <v>250.9501037597656</v>
+      <c r="C417">
+        <v>250.95</v>
       </c>
       <c r="D417">
         <v>194.62187194824219</v>
@@ -8856,8 +8856,8 @@
       <c r="B418" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="C418" s="5">
-        <v>199.5856628417969</v>
+      <c r="C418">
+        <v>230.12</v>
       </c>
       <c r="D418">
         <v>163.36991882324219</v>
@@ -8870,8 +8870,8 @@
       <c r="B419" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="C419" s="5">
-        <v>147.5632629394531</v>
+      <c r="C419">
+        <v>172.38</v>
       </c>
       <c r="D419">
         <v>134.74822998046881</v>
@@ -8884,8 +8884,8 @@
       <c r="B420" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="C420" s="5">
-        <v>217.99504089355469</v>
+      <c r="C420">
+        <v>218</v>
       </c>
       <c r="D420">
         <v>171.90419006347659</v>
@@ -8898,8 +8898,8 @@
       <c r="B421" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="C421" s="5">
-        <v>237.61767578125</v>
+      <c r="C421">
+        <v>237.62</v>
       </c>
       <c r="D421">
         <v>194.1744689941406</v>
@@ -8912,7 +8912,7 @@
       <c r="B422" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C422" s="5">
+      <c r="C422">
         <v>341</v>
       </c>
     </row>
@@ -8923,8 +8923,8 @@
       <c r="B423" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="C423" s="5">
-        <v>333.10977172851562</v>
+      <c r="C423">
+        <v>333.11</v>
       </c>
       <c r="D423">
         <v>288.059814453125</v>
@@ -8937,8 +8937,8 @@
       <c r="B424" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="C424" s="5">
-        <v>349.76165771484381</v>
+      <c r="C424">
+        <v>349.76</v>
       </c>
       <c r="D424">
         <v>292.54043579101562</v>
@@ -8951,8 +8951,8 @@
       <c r="B425" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="C425" s="5">
-        <v>294.70730590820312</v>
+      <c r="C425">
+        <v>339.8</v>
       </c>
       <c r="D425">
         <v>253.53521728515619</v>
@@ -8965,8 +8965,8 @@
       <c r="B426" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="C426" s="5">
-        <v>247.36021423339841</v>
+      <c r="C426">
+        <v>288.97000000000003</v>
       </c>
       <c r="D426">
         <v>231.5208435058594</v>
@@ -8979,8 +8979,8 @@
       <c r="B427" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="C427" s="5">
-        <v>333.71011352539062</v>
+      <c r="C427">
+        <v>333.71</v>
       </c>
       <c r="D427">
         <v>265.06680297851562</v>
@@ -8993,8 +8993,8 @@
       <c r="B428" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="C428" s="5">
-        <v>347.288330078125</v>
+      <c r="C428">
+        <v>347.29</v>
       </c>
       <c r="D428">
         <v>302.63449096679688</v>
@@ -9007,7 +9007,7 @@
       <c r="B429" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C429" s="5">
+      <c r="C429">
         <v>26</v>
       </c>
     </row>
@@ -9018,8 +9018,8 @@
       <c r="B430" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C430" s="5">
-        <v>25.982748031616211</v>
+      <c r="C430">
+        <v>25.98</v>
       </c>
       <c r="D430">
         <v>23.255369186401371</v>
@@ -9032,8 +9032,8 @@
       <c r="B431" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C431" s="5">
-        <v>24.73587608337402</v>
+      <c r="C431">
+        <v>24.74</v>
       </c>
       <c r="D431">
         <v>23.672250747680661</v>
@@ -9046,8 +9046,8 @@
       <c r="B432" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C432" s="5">
-        <v>24.089801788330082</v>
+      <c r="C432">
+        <v>27.78</v>
       </c>
       <c r="D432">
         <v>22.09721565246582</v>
@@ -9060,8 +9060,8 @@
       <c r="B433" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C433" s="5">
-        <v>24.048191070556641</v>
+      <c r="C433">
+        <v>28.09</v>
       </c>
       <c r="D433">
         <v>22.67573356628418</v>
@@ -9074,8 +9074,8 @@
       <c r="B434" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C434" s="5">
-        <v>26.10238075256348</v>
+      <c r="C434">
+        <v>26.1</v>
       </c>
       <c r="D434">
         <v>23.702846527099609</v>
@@ -9088,8 +9088,8 @@
       <c r="B435" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C435" s="5">
-        <v>25.588827133178711</v>
+      <c r="C435">
+        <v>25.59</v>
       </c>
       <c r="D435">
         <v>22.193588256835941</v>
@@ -9102,7 +9102,7 @@
       <c r="B436" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C436" s="5">
+      <c r="C436">
         <v>317</v>
       </c>
     </row>
@@ -9113,8 +9113,8 @@
       <c r="B437" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C437" s="5">
-        <v>363.65353393554688</v>
+      <c r="C437">
+        <v>363.65</v>
       </c>
       <c r="D437">
         <v>300.00836181640619</v>
@@ -9127,8 +9127,8 @@
       <c r="B438" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C438" s="5">
-        <v>377.0118408203125</v>
+      <c r="C438">
+        <v>377.01</v>
       </c>
       <c r="D438">
         <v>312.49716186523438</v>
@@ -9141,8 +9141,8 @@
       <c r="B439" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C439" s="5">
-        <v>277.150390625</v>
+      <c r="C439">
+        <v>319.56</v>
       </c>
       <c r="D439">
         <v>232.94035339355469</v>
@@ -9155,8 +9155,8 @@
       <c r="B440" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C440" s="5">
-        <v>214.23548889160159</v>
+      <c r="C440">
+        <v>250.27</v>
       </c>
       <c r="D440">
         <v>183.12937927246091</v>
@@ -9169,8 +9169,8 @@
       <c r="B441" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C441" s="5">
-        <v>321.2421875</v>
+      <c r="C441">
+        <v>321.24</v>
       </c>
       <c r="D441">
         <v>234.9892272949219</v>
@@ -9183,8 +9183,8 @@
       <c r="B442" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C442" s="5">
-        <v>343.95364379882812</v>
+      <c r="C442">
+        <v>343.95</v>
       </c>
       <c r="D442">
         <v>293.38314819335938</v>
@@ -9197,7 +9197,7 @@
       <c r="B443" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C443" s="5">
+      <c r="C443">
         <v>422</v>
       </c>
     </row>
@@ -9208,8 +9208,8 @@
       <c r="B444" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C444" s="5">
-        <v>431.13272094726562</v>
+      <c r="C444">
+        <v>431.13</v>
       </c>
       <c r="D444">
         <v>364.97988891601562</v>
@@ -9222,8 +9222,8 @@
       <c r="B445" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C445" s="5">
-        <v>455.947265625</v>
+      <c r="C445">
+        <v>455.95</v>
       </c>
       <c r="D445">
         <v>379.89016723632812</v>
@@ -9236,8 +9236,8 @@
       <c r="B446" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C446" s="5">
-        <v>395.14810180664062</v>
+      <c r="C446">
+        <v>455.61</v>
       </c>
       <c r="D446">
         <v>303.43792724609381</v>
@@ -9250,8 +9250,8 @@
       <c r="B447" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C447" s="5">
-        <v>287.10098266601562</v>
+      <c r="C447">
+        <v>335.39</v>
       </c>
       <c r="D447">
         <v>252.16499328613281</v>
@@ -9264,8 +9264,8 @@
       <c r="B448" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C448" s="5">
-        <v>398.44137573242188</v>
+      <c r="C448">
+        <v>398.44</v>
       </c>
       <c r="D448">
         <v>322.5111083984375</v>
@@ -9278,8 +9278,8 @@
       <c r="B449" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C449" s="5">
-        <v>428.21023559570312</v>
+      <c r="C449">
+        <v>428.21</v>
       </c>
       <c r="D449">
         <v>366.69287109375</v>
@@ -9292,7 +9292,7 @@
       <c r="B450" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C450" s="5">
+      <c r="C450">
         <v>243</v>
       </c>
     </row>
@@ -9303,8 +9303,8 @@
       <c r="B451" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C451" s="5">
-        <v>233.2763671875</v>
+      <c r="C451">
+        <v>233.28</v>
       </c>
       <c r="D451">
         <v>191.29566955566409</v>
@@ -9317,8 +9317,8 @@
       <c r="B452" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C452" s="5">
-        <v>328.73721313476562</v>
+      <c r="C452">
+        <v>328.74</v>
       </c>
       <c r="D452">
         <v>282.55136108398438</v>
@@ -9331,8 +9331,8 @@
       <c r="B453" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C453" s="5">
-        <v>275.79672241210938</v>
+      <c r="C453">
+        <v>318</v>
       </c>
       <c r="D453">
         <v>259.86102294921881</v>
@@ -9345,8 +9345,8 @@
       <c r="B454" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C454" s="5">
-        <v>222.0338134765625</v>
+      <c r="C454">
+        <v>259.38</v>
       </c>
       <c r="D454">
         <v>213.7664489746094</v>
@@ -9359,8 +9359,8 @@
       <c r="B455" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C455" s="5">
-        <v>295.37289428710938</v>
+      <c r="C455">
+        <v>295.37</v>
       </c>
       <c r="D455">
         <v>265.91921997070312</v>
@@ -9373,8 +9373,8 @@
       <c r="B456" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C456" s="5">
-        <v>441.565673828125</v>
+      <c r="C456">
+        <v>441.57</v>
       </c>
       <c r="D456">
         <v>350.48294067382812</v>
@@ -9387,7 +9387,7 @@
       <c r="B457" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="C457" s="5">
+      <c r="C457">
         <v>406</v>
       </c>
       <c r="D457">
@@ -9401,7 +9401,7 @@
       <c r="B458" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C458" s="5">
+      <c r="C458">
         <v>415</v>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       <c r="B459" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="C459" s="5">
+      <c r="C459">
         <v>416</v>
       </c>
       <c r="D459">
@@ -9426,7 +9426,7 @@
       <c r="B460" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="C460" s="5">
+      <c r="C460">
         <v>399</v>
       </c>
       <c r="D460">
@@ -9440,8 +9440,8 @@
       <c r="B461" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="C461" s="5">
-        <v>316</v>
+      <c r="C461">
+        <v>364.35</v>
       </c>
       <c r="D461">
         <v>0</v>
@@ -9454,8 +9454,8 @@
       <c r="B462" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="C462" s="5">
-        <v>266</v>
+      <c r="C462">
+        <v>310.74</v>
       </c>
       <c r="D462">
         <v>0</v>
@@ -9468,7 +9468,7 @@
       <c r="B463" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="C463" s="5">
+      <c r="C463">
         <v>368</v>
       </c>
       <c r="D463">
@@ -9482,7 +9482,7 @@
       <c r="B464" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="C464" s="5">
+      <c r="C464">
         <v>382</v>
       </c>
       <c r="D464">
@@ -9496,7 +9496,7 @@
       <c r="B465" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C465" s="5">
+      <c r="C465">
         <v>364</v>
       </c>
     </row>
@@ -9507,8 +9507,8 @@
       <c r="B466" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="C466" s="5">
-        <v>380.00262451171881</v>
+      <c r="C466">
+        <v>380</v>
       </c>
       <c r="D466">
         <v>296.99774169921881</v>
@@ -9521,8 +9521,8 @@
       <c r="B467" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="C467" s="5">
-        <v>389.67294311523438</v>
+      <c r="C467">
+        <v>389.67</v>
       </c>
       <c r="D467">
         <v>317.42431640625</v>
@@ -9535,8 +9535,8 @@
       <c r="B468" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="C468" s="5">
-        <v>311.231201171875</v>
+      <c r="C468">
+        <v>358.85</v>
       </c>
       <c r="D468">
         <v>259.8773193359375</v>
@@ -9549,8 +9549,8 @@
       <c r="B469" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="C469" s="5">
-        <v>285.75985717773438</v>
+      <c r="C469">
+        <v>333.83</v>
       </c>
       <c r="D469">
         <v>243.7053527832031</v>
@@ -9563,8 +9563,8 @@
       <c r="B470" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="C470" s="5">
-        <v>391.89849853515619</v>
+      <c r="C470">
+        <v>391.9</v>
       </c>
       <c r="D470">
         <v>307.23049926757812</v>
@@ -9577,8 +9577,8 @@
       <c r="B471" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="C471" s="5">
-        <v>379.86639404296881</v>
+      <c r="C471">
+        <v>379.87</v>
       </c>
       <c r="D471">
         <v>330.6112060546875</v>
@@ -9591,7 +9591,7 @@
       <c r="B472" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="C472" s="5">
+      <c r="C472">
         <v>53</v>
       </c>
       <c r="D472">
@@ -9605,7 +9605,7 @@
       <c r="B473" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C473" s="5">
+      <c r="C473">
         <v>49</v>
       </c>
     </row>
@@ -9616,7 +9616,7 @@
       <c r="B474" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="C474" s="5">
+      <c r="C474">
         <v>54</v>
       </c>
       <c r="D474">
@@ -9630,7 +9630,7 @@
       <c r="B475" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="C475" s="5">
+      <c r="C475">
         <v>52</v>
       </c>
       <c r="D475">
@@ -9644,8 +9644,8 @@
       <c r="B476" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="C476" s="5">
-        <v>41</v>
+      <c r="C476">
+        <v>47.27</v>
       </c>
       <c r="D476">
         <v>0</v>
@@ -9658,8 +9658,8 @@
       <c r="B477" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="C477" s="5">
-        <v>35</v>
+      <c r="C477">
+        <v>40.89</v>
       </c>
       <c r="D477">
         <v>0</v>
@@ -9672,7 +9672,7 @@
       <c r="B478" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="C478" s="5">
+      <c r="C478">
         <v>48</v>
       </c>
       <c r="D478">
@@ -9686,7 +9686,7 @@
       <c r="B479" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="C479" s="5">
+      <c r="C479">
         <v>50</v>
       </c>
       <c r="D479">
@@ -9700,7 +9700,7 @@
       <c r="B480" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C480" s="5">
+      <c r="C480">
         <v>17</v>
       </c>
     </row>
@@ -9711,8 +9711,8 @@
       <c r="B481" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C481" s="5">
-        <v>16.33277702331543</v>
+      <c r="C481">
+        <v>16.329999999999998</v>
       </c>
       <c r="D481">
         <v>14.13308906555176</v>
@@ -9725,8 +9725,8 @@
       <c r="B482" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C482" s="5">
-        <v>16.747035980224609</v>
+      <c r="C482">
+        <v>16.75</v>
       </c>
       <c r="D482">
         <v>14.09735012054443</v>
@@ -9739,8 +9739,8 @@
       <c r="B483" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C483" s="5">
-        <v>17.356746673583981</v>
+      <c r="C483">
+        <v>20.010000000000002</v>
       </c>
       <c r="D483">
         <v>15.393528938293461</v>
@@ -9753,8 +9753,8 @@
       <c r="B484" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C484" s="5">
-        <v>19.397747039794918</v>
+      <c r="C484">
+        <v>22.66</v>
       </c>
       <c r="D484">
         <v>16.156991958618161</v>
@@ -9767,8 +9767,8 @@
       <c r="B485" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C485" s="5">
-        <v>16.547744750976559</v>
+      <c r="C485">
+        <v>16.55</v>
       </c>
       <c r="D485">
         <v>13.961287498474119</v>
@@ -9781,8 +9781,8 @@
       <c r="B486" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C486" s="5">
-        <v>16.516530990600589</v>
+      <c r="C486">
+        <v>16.52</v>
       </c>
       <c r="D486">
         <v>13.86273097991943</v>
@@ -9795,7 +9795,7 @@
       <c r="B487" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C487" s="5">
+      <c r="C487">
         <v>210</v>
       </c>
     </row>
@@ -9806,8 +9806,8 @@
       <c r="B488" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="C488" s="5">
-        <v>215.92732238769531</v>
+      <c r="C488">
+        <v>215.93</v>
       </c>
       <c r="D488">
         <v>170.81028747558591</v>
@@ -9820,8 +9820,8 @@
       <c r="B489" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="C489" s="5">
-        <v>233.79753112792969</v>
+      <c r="C489">
+        <v>233.8</v>
       </c>
       <c r="D489">
         <v>183.3706359863281</v>
@@ -9834,8 +9834,8 @@
       <c r="B490" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="C490" s="5">
-        <v>193.452392578125</v>
+      <c r="C490">
+        <v>223.05</v>
       </c>
       <c r="D490">
         <v>160.9730529785156</v>
@@ -9848,8 +9848,8 @@
       <c r="B491" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="C491" s="5">
-        <v>147.74281311035159</v>
+      <c r="C491">
+        <v>172.59</v>
       </c>
       <c r="D491">
         <v>130.94123840332031</v>
@@ -9862,8 +9862,8 @@
       <c r="B492" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="C492" s="5">
-        <v>208.31965637207031</v>
+      <c r="C492">
+        <v>208.32</v>
       </c>
       <c r="D492">
         <v>164.5888671875</v>
@@ -9876,8 +9876,8 @@
       <c r="B493" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="C493" s="5">
-        <v>221.65924072265619</v>
+      <c r="C493">
+        <v>221.66</v>
       </c>
       <c r="D493">
         <v>188.79716491699219</v>
@@ -9890,7 +9890,7 @@
       <c r="B494" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C494" s="5">
+      <c r="C494">
         <v>463</v>
       </c>
     </row>
@@ -9901,8 +9901,8 @@
       <c r="B495" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="C495" s="5">
-        <v>550.82293701171875</v>
+      <c r="C495">
+        <v>550.82000000000005</v>
       </c>
       <c r="D495">
         <v>471.17202758789062</v>
@@ -9915,8 +9915,8 @@
       <c r="B496" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="C496" s="5">
-        <v>499.97064208984381</v>
+      <c r="C496">
+        <v>499.97</v>
       </c>
       <c r="D496">
         <v>414.923095703125</v>
@@ -9929,8 +9929,8 @@
       <c r="B497" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="C497" s="5">
-        <v>405.91470336914062</v>
+      <c r="C497">
+        <v>468.02</v>
       </c>
       <c r="D497">
         <v>378.71633911132812</v>
@@ -9943,8 +9943,8 @@
       <c r="B498" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="C498" s="5">
-        <v>337.83456420898438</v>
+      <c r="C498">
+        <v>394.66</v>
       </c>
       <c r="D498">
         <v>323.11715698242188</v>
@@ -9957,8 +9957,8 @@
       <c r="B499" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="C499" s="5">
-        <v>486.10415649414062</v>
+      <c r="C499">
+        <v>486.1</v>
       </c>
       <c r="D499">
         <v>390.528564453125</v>
@@ -9971,8 +9971,8 @@
       <c r="B500" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="C500" s="5">
-        <v>504.83383178710938</v>
+      <c r="C500">
+        <v>504.83</v>
       </c>
       <c r="D500">
         <v>426.93502807617188</v>
@@ -9985,7 +9985,7 @@
       <c r="B501" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C501" s="5">
+      <c r="C501">
         <v>115</v>
       </c>
     </row>
@@ -9996,8 +9996,8 @@
       <c r="B502" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="C502" s="5">
-        <v>101.9977340698242</v>
+      <c r="C502">
+        <v>102</v>
       </c>
       <c r="D502">
         <v>74.632545471191406</v>
@@ -10010,8 +10010,8 @@
       <c r="B503" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="C503" s="5">
-        <v>107.82163238525391</v>
+      <c r="C503">
+        <v>107.82</v>
       </c>
       <c r="D503">
         <v>81.759620666503906</v>
@@ -10024,8 +10024,8 @@
       <c r="B504" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="C504" s="5">
-        <v>82.780014038085938</v>
+      <c r="C504">
+        <v>95.45</v>
       </c>
       <c r="D504">
         <v>64.833702087402344</v>
@@ -10038,8 +10038,8 @@
       <c r="B505" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="C505" s="5">
-        <v>63.1767578125</v>
+      <c r="C505">
+        <v>73.8</v>
       </c>
       <c r="D505">
         <v>52.129726409912109</v>
@@ -10052,8 +10052,8 @@
       <c r="B506" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="C506" s="5">
-        <v>101.3410339355469</v>
+      <c r="C506">
+        <v>101.34</v>
       </c>
       <c r="D506">
         <v>75.118232727050781</v>
@@ -10066,8 +10066,8 @@
       <c r="B507" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="C507" s="5">
-        <v>95.992774963378906</v>
+      <c r="C507">
+        <v>95.99</v>
       </c>
       <c r="D507">
         <v>68.497817993164062</v>
@@ -10080,7 +10080,7 @@
       <c r="B508" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C508" s="5">
+      <c r="C508">
         <v>151</v>
       </c>
     </row>
@@ -10091,8 +10091,8 @@
       <c r="B509" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="C509" s="5">
-        <v>116.3666915893555</v>
+      <c r="C509">
+        <v>116.37</v>
       </c>
       <c r="D509">
         <v>94.203750610351562</v>
@@ -10105,8 +10105,8 @@
       <c r="B510" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="C510" s="5">
-        <v>109.6280212402344</v>
+      <c r="C510">
+        <v>109.63</v>
       </c>
       <c r="D510">
         <v>81.347671508789062</v>
@@ -10119,8 +10119,8 @@
       <c r="B511" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="C511" s="5">
-        <v>104.78900146484381</v>
+      <c r="C511">
+        <v>120.82</v>
       </c>
       <c r="D511">
         <v>84.6220703125</v>
@@ -10133,8 +10133,8 @@
       <c r="B512" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="C512" s="5">
-        <v>86.402374267578125</v>
+      <c r="C512">
+        <v>100.94</v>
       </c>
       <c r="D512">
         <v>71.665885925292969</v>
@@ -10147,8 +10147,8 @@
       <c r="B513" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="C513" s="5">
-        <v>110.32106781005859</v>
+      <c r="C513">
+        <v>110.32</v>
       </c>
       <c r="D513">
         <v>85.580520629882812</v>
@@ -10161,8 +10161,8 @@
       <c r="B514" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="C514" s="5">
-        <v>118.9295349121094</v>
+      <c r="C514">
+        <v>118.93</v>
       </c>
       <c r="D514">
         <v>101.7806854248047</v>
@@ -10175,7 +10175,7 @@
       <c r="B515" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C515" s="5">
+      <c r="C515">
         <v>68</v>
       </c>
     </row>
@@ -10186,8 +10186,8 @@
       <c r="B516" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C516" s="5">
-        <v>75.613822937011719</v>
+      <c r="C516">
+        <v>75.61</v>
       </c>
       <c r="D516">
         <v>56.365016937255859</v>
@@ -10200,8 +10200,8 @@
       <c r="B517" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C517" s="5">
-        <v>74.858573913574219</v>
+      <c r="C517">
+        <v>74.86</v>
       </c>
       <c r="D517">
         <v>58.151756286621087</v>
@@ -10214,8 +10214,8 @@
       <c r="B518" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C518" s="5">
-        <v>54.030906677246087</v>
+      <c r="C518">
+        <v>62.3</v>
       </c>
       <c r="D518">
         <v>44.970233917236328</v>
@@ -10228,8 +10228,8 @@
       <c r="B519" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C519" s="5">
-        <v>49.135654449462891</v>
+      <c r="C519">
+        <v>57.4</v>
       </c>
       <c r="D519">
         <v>41.920215606689453</v>
@@ -10242,8 +10242,8 @@
       <c r="B520" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C520" s="5">
-        <v>65.687110900878906</v>
+      <c r="C520">
+        <v>65.69</v>
       </c>
       <c r="D520">
         <v>50.87274169921875</v>
@@ -10256,8 +10256,8 @@
       <c r="B521" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C521" s="5">
-        <v>71.907341003417969</v>
+      <c r="C521">
+        <v>71.91</v>
       </c>
       <c r="D521">
         <v>57.044956207275391</v>
@@ -10270,7 +10270,7 @@
       <c r="B522" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C522" s="5">
+      <c r="C522">
         <v>189</v>
       </c>
     </row>
@@ -10281,8 +10281,8 @@
       <c r="B523" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="C523" s="5">
-        <v>164.22077941894531</v>
+      <c r="C523">
+        <v>164.22</v>
       </c>
       <c r="D523">
         <v>136.2034606933594</v>
@@ -10295,8 +10295,8 @@
       <c r="B524" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="C524" s="5">
-        <v>169.07450866699219</v>
+      <c r="C524">
+        <v>169.07</v>
       </c>
       <c r="D524">
         <v>141.09309387207031</v>
@@ -10309,8 +10309,8 @@
       <c r="B525" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="C525" s="5">
-        <v>141.07716369628909</v>
+      <c r="C525">
+        <v>162.66</v>
       </c>
       <c r="D525">
         <v>120.77772521972661</v>
@@ -10323,8 +10323,8 @@
       <c r="B526" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="C526" s="5">
-        <v>116.9359970092773</v>
+      <c r="C526">
+        <v>136.61000000000001</v>
       </c>
       <c r="D526">
         <v>103.23484802246089</v>
@@ -10337,8 +10337,8 @@
       <c r="B527" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="C527" s="5">
-        <v>172.13543701171881</v>
+      <c r="C527">
+        <v>172.14</v>
       </c>
       <c r="D527">
         <v>135.8037109375</v>
@@ -10351,8 +10351,8 @@
       <c r="B528" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="C528" s="5">
-        <v>165.69767761230469</v>
+      <c r="C528">
+        <v>165.7</v>
       </c>
       <c r="D528">
         <v>134.16845703125</v>
